--- a/roadline-geojson/千歳出張所管内.xlsx
+++ b/roadline-geojson/千歳出張所管内.xlsx
@@ -8,455 +8,845 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365tsukuba-my.sharepoint.com/personal/s1911313_u_tsukuba_ac_jp/Documents/GitHub/roadline-geojson/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52AAF4EA-A159-CE47-830E-22E66FA61587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_0308E1D0DCCF039F0F11523A0B15022EE2268834" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9404EDB-5BD7-2247-B1D3-A45FEF448323}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{861469B9-6669-254B-B64D-5D0ACAAEB095}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="29400" windowHeight="16660" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1077 千歳インター線" sheetId="1" r:id="rId1"/>
     <sheet name="3369 島松停車場線" sheetId="2" r:id="rId2"/>
     <sheet name="3371 北広島停車場線" sheetId="3" r:id="rId3"/>
+    <sheet name="3370 丸駒線" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
+    <sheet name="Restored" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="274">
+  <si>
+    <t>図面番号</t>
+  </si>
+  <si>
+    <t>L-座標番号</t>
+  </si>
+  <si>
+    <t>L-X座標</t>
+  </si>
+  <si>
+    <t>L-Y座標</t>
+  </si>
+  <si>
+    <t>L-幅員</t>
+  </si>
+  <si>
+    <t>L-備考</t>
+  </si>
+  <si>
+    <t>R-座標番号</t>
+  </si>
+  <si>
+    <t>R-X座標</t>
+  </si>
+  <si>
+    <t>R-Y座標</t>
+  </si>
+  <si>
+    <t>R-幅員</t>
+  </si>
+  <si>
+    <t>R-備考</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>L-1</t>
+  </si>
+  <si>
+    <t>R-1</t>
+  </si>
+  <si>
+    <t>L-2</t>
+  </si>
+  <si>
+    <t>R-2</t>
+  </si>
+  <si>
+    <t>L-3</t>
+  </si>
+  <si>
+    <t>R-3</t>
+  </si>
+  <si>
+    <t>L-4</t>
+  </si>
+  <si>
+    <t>R-4</t>
+  </si>
+  <si>
+    <t>L-5</t>
+  </si>
+  <si>
+    <t>R-5</t>
+  </si>
+  <si>
+    <t>L-6</t>
+  </si>
+  <si>
+    <t>R-6</t>
+  </si>
+  <si>
+    <t>L-7</t>
+  </si>
+  <si>
+    <t>R-7</t>
+  </si>
+  <si>
+    <t>L-8</t>
+  </si>
+  <si>
+    <t>R-8</t>
+  </si>
+  <si>
+    <t>L-9</t>
+  </si>
+  <si>
+    <t>R-9</t>
+  </si>
+  <si>
+    <t>L-10</t>
+  </si>
+  <si>
+    <t>R-10</t>
+  </si>
+  <si>
+    <t>L-11</t>
+  </si>
+  <si>
+    <t>R-11</t>
+  </si>
+  <si>
+    <t>L-12</t>
+  </si>
+  <si>
+    <t>R-12</t>
+  </si>
+  <si>
+    <t>L-13</t>
+  </si>
+  <si>
+    <t>R-13</t>
+  </si>
+  <si>
+    <t>L-14</t>
+  </si>
+  <si>
+    <t>R-14</t>
+  </si>
+  <si>
+    <t>L-15</t>
+  </si>
+  <si>
+    <t>R-15</t>
+  </si>
+  <si>
+    <t>L-16</t>
+  </si>
+  <si>
+    <t>R-16</t>
+  </si>
+  <si>
+    <t>L-17</t>
+  </si>
+  <si>
+    <t>R-17</t>
+  </si>
+  <si>
+    <t>L-18</t>
+  </si>
+  <si>
+    <t>R-18</t>
+  </si>
+  <si>
+    <t>L-19</t>
+  </si>
+  <si>
+    <t>R-19</t>
+  </si>
+  <si>
+    <t>L-20</t>
+  </si>
+  <si>
+    <t>R-20</t>
+  </si>
+  <si>
+    <t>L-21</t>
+  </si>
+  <si>
+    <t>R-21</t>
+  </si>
+  <si>
+    <t>L-22</t>
+  </si>
+  <si>
+    <t>R-22</t>
+  </si>
+  <si>
+    <t>L-23</t>
+  </si>
+  <si>
+    <t>R-23</t>
+  </si>
+  <si>
+    <t>L-24</t>
+  </si>
+  <si>
+    <t>R-24</t>
+  </si>
+  <si>
+    <t>L-25</t>
+  </si>
+  <si>
+    <t>R-25</t>
+  </si>
+  <si>
+    <t>L-26</t>
+  </si>
+  <si>
+    <t>R-26</t>
+  </si>
+  <si>
+    <t>L-27</t>
+  </si>
+  <si>
+    <t>R-27</t>
+  </si>
+  <si>
+    <t>L-28</t>
+  </si>
+  <si>
+    <t>R-28</t>
+  </si>
+  <si>
+    <t>L-29</t>
+  </si>
+  <si>
+    <t>R-29</t>
+  </si>
+  <si>
+    <t>L-30</t>
+  </si>
+  <si>
+    <t>R-30</t>
+  </si>
+  <si>
+    <t>L-31</t>
+  </si>
+  <si>
+    <t>R-31</t>
+  </si>
+  <si>
+    <t>L-32</t>
+  </si>
+  <si>
+    <t>R-32</t>
+  </si>
+  <si>
+    <t>L-33</t>
+  </si>
+  <si>
+    <t>R-33</t>
+  </si>
+  <si>
+    <t>L-34</t>
+  </si>
+  <si>
+    <t>R-34</t>
+  </si>
+  <si>
+    <t>L-35</t>
+  </si>
+  <si>
+    <t>R-35</t>
+  </si>
+  <si>
+    <t>L-36</t>
+  </si>
+  <si>
+    <t>R-36</t>
+  </si>
+  <si>
+    <t>L-37</t>
+  </si>
+  <si>
+    <t>R-37</t>
+  </si>
+  <si>
+    <t>L-38</t>
+  </si>
+  <si>
+    <t>R-3B</t>
+  </si>
+  <si>
+    <t>L-39</t>
+  </si>
+  <si>
+    <t>R-39</t>
+  </si>
+  <si>
+    <t>L-40</t>
+  </si>
+  <si>
+    <t>R-40</t>
+  </si>
+  <si>
+    <t>L-41</t>
+  </si>
+  <si>
+    <t>R-41</t>
+  </si>
+  <si>
+    <t>L-42</t>
+  </si>
+  <si>
+    <t>R-42</t>
+  </si>
+  <si>
+    <t>L-43</t>
+  </si>
+  <si>
+    <t>R-43</t>
+  </si>
+  <si>
+    <t>L-43-1</t>
+  </si>
+  <si>
+    <t>R-44</t>
+  </si>
+  <si>
+    <t>L-43-2</t>
+  </si>
+  <si>
+    <t>R-45</t>
+  </si>
+  <si>
+    <t>L-44</t>
+  </si>
+  <si>
+    <t>R-46</t>
+  </si>
+  <si>
+    <t>L-45</t>
+  </si>
+  <si>
+    <t>R-47</t>
+  </si>
+  <si>
+    <t>L-46</t>
+  </si>
+  <si>
+    <t>L-46-1</t>
+  </si>
+  <si>
+    <t>L-46-2</t>
+  </si>
+  <si>
+    <t>L-47</t>
+  </si>
+  <si>
+    <t>L-48</t>
+  </si>
+  <si>
+    <t>L-49</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>外れ値のためR-7, 8除外</t>
+  </si>
+  <si>
+    <t>外れ値のためL-24除外</t>
+  </si>
   <si>
     <t>L-29座標欠損</t>
-    <rPh sb="4" eb="8">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-30</t>
-  </si>
-  <si>
-    <t>1-2</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-28</t>
-  </si>
-  <si>
-    <t>L-27</t>
-  </si>
-  <si>
-    <t>L-26</t>
-  </si>
-  <si>
-    <t>外れ値のためL-24除外</t>
-    <rPh sb="0" eb="1">
-      <t>ハズレティ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジョガイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-25</t>
-  </si>
-  <si>
-    <t>L-23</t>
-  </si>
-  <si>
-    <t>L-22</t>
-  </si>
-  <si>
-    <t>L-21</t>
-  </si>
-  <si>
-    <t>L-20</t>
-  </si>
-  <si>
-    <t>L-19</t>
-  </si>
-  <si>
-    <t>L-18</t>
-  </si>
-  <si>
-    <t>L-17</t>
-  </si>
-  <si>
-    <t>L-16</t>
-  </si>
-  <si>
-    <t>R-15</t>
-  </si>
-  <si>
-    <t>L-15</t>
-  </si>
-  <si>
-    <t>R-14</t>
-  </si>
-  <si>
-    <t>L-14</t>
-  </si>
-  <si>
-    <t>R-13</t>
-  </si>
-  <si>
-    <t>L-13</t>
-  </si>
-  <si>
-    <t>R-12</t>
-  </si>
-  <si>
-    <t>L-12</t>
-  </si>
-  <si>
-    <t>R-11</t>
-  </si>
-  <si>
-    <t>L-11</t>
-  </si>
-  <si>
-    <t>R-10</t>
-  </si>
-  <si>
-    <t>L-10</t>
-  </si>
-  <si>
-    <t>外れ値のためR-7, 8除外</t>
-    <rPh sb="0" eb="1">
-      <t>ハズレティ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ジョガイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R-9</t>
-  </si>
-  <si>
-    <t>L-9</t>
-  </si>
-  <si>
-    <t>L-8</t>
-  </si>
-  <si>
-    <t>L-7</t>
-  </si>
-  <si>
-    <t>R-6</t>
-  </si>
-  <si>
-    <t>L-6</t>
-  </si>
-  <si>
-    <t>R-5</t>
-  </si>
-  <si>
-    <t>L-5</t>
-  </si>
-  <si>
-    <t>R-4</t>
-  </si>
-  <si>
-    <t>L-4</t>
-  </si>
-  <si>
-    <t>R-3</t>
-  </si>
-  <si>
-    <t>L-3</t>
-  </si>
-  <si>
-    <t>R-2</t>
-  </si>
-  <si>
-    <t>L-2</t>
-  </si>
-  <si>
-    <t>R-1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-49</t>
   </si>
   <si>
     <t>1-1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-48</t>
-  </si>
-  <si>
-    <t>L-47</t>
-  </si>
-  <si>
-    <t>L-46-2</t>
-  </si>
-  <si>
-    <t>L-46-1</t>
-  </si>
-  <si>
-    <t>L-46</t>
-  </si>
-  <si>
-    <t>R-47</t>
-  </si>
-  <si>
-    <t>L-45</t>
-  </si>
-  <si>
-    <t>R-46</t>
-  </si>
-  <si>
-    <t>L-44</t>
-  </si>
-  <si>
-    <t>R-45</t>
-  </si>
-  <si>
-    <t>L-43-2</t>
-  </si>
-  <si>
-    <t>R-44</t>
-  </si>
-  <si>
-    <t>L-43-1</t>
-  </si>
-  <si>
-    <t>R-43</t>
-  </si>
-  <si>
-    <t>L-43</t>
-  </si>
-  <si>
-    <t>R-42</t>
-  </si>
-  <si>
-    <t>L-42</t>
-  </si>
-  <si>
-    <t>R-41</t>
-  </si>
-  <si>
-    <t>L-41</t>
-  </si>
-  <si>
-    <t>R-40</t>
-  </si>
-  <si>
-    <t>L-40</t>
-  </si>
-  <si>
-    <t>R-39</t>
-  </si>
-  <si>
-    <t>L-39</t>
-  </si>
-  <si>
-    <t>R-3B</t>
-  </si>
-  <si>
-    <t>L-38</t>
-  </si>
-  <si>
-    <t>R-37</t>
-  </si>
-  <si>
-    <t>L-37</t>
-  </si>
-  <si>
-    <t>R-36</t>
-  </si>
-  <si>
-    <t>L-36</t>
-  </si>
-  <si>
-    <t>R-35</t>
-  </si>
-  <si>
-    <t>L-35</t>
-  </si>
-  <si>
-    <t>R-34</t>
-  </si>
-  <si>
-    <t>L-34</t>
-  </si>
-  <si>
-    <t>R-33</t>
-  </si>
-  <si>
-    <t>L-33</t>
-  </si>
-  <si>
-    <t>R-32</t>
-  </si>
-  <si>
-    <t>L-32</t>
-  </si>
-  <si>
-    <t>R-31</t>
-  </si>
-  <si>
-    <t>L-31</t>
-  </si>
-  <si>
-    <t>R-30</t>
-  </si>
-  <si>
-    <t>R-29</t>
-  </si>
-  <si>
-    <t>L-29</t>
-  </si>
-  <si>
-    <t>R-28</t>
-  </si>
-  <si>
-    <t>R-27</t>
-  </si>
-  <si>
-    <t>R-26</t>
-  </si>
-  <si>
-    <t>R-25</t>
-  </si>
-  <si>
-    <t>R-24</t>
-  </si>
-  <si>
-    <t>L-24</t>
-  </si>
-  <si>
-    <t>R-23</t>
-  </si>
-  <si>
-    <t>R-22</t>
-  </si>
-  <si>
-    <t>R-21</t>
-  </si>
-  <si>
-    <t>R-20</t>
-  </si>
-  <si>
-    <t>R-19</t>
-  </si>
-  <si>
-    <t>R-18</t>
-  </si>
-  <si>
-    <t>R-17</t>
-  </si>
-  <si>
-    <t>R-16</t>
-  </si>
-  <si>
-    <t>R-8</t>
-  </si>
-  <si>
-    <t>R-7</t>
-  </si>
-  <si>
-    <t>R-1</t>
-  </si>
-  <si>
-    <t>L-1</t>
-  </si>
-  <si>
-    <t>R-備考</t>
-    <rPh sb="2" eb="4">
-      <t>ビコウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R-幅員</t>
-    <rPh sb="2" eb="4">
-      <t>フクイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R-Y座標</t>
-    <rPh sb="3" eb="5">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R-X座標</t>
-    <rPh sb="3" eb="5">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R-座標番号</t>
-    <rPh sb="2" eb="6">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-備考</t>
-    <rPh sb="2" eb="4">
-      <t>ビコウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-幅員</t>
-    <rPh sb="2" eb="4">
-      <t>フク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-Y座標</t>
-    <rPh sb="3" eb="5">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-X座標</t>
-    <rPh sb="3" eb="5">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-座標番号</t>
-    <rPh sb="2" eb="6">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>図面番号</t>
-    <rPh sb="0" eb="4">
-      <t>ズメn</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>R-38</t>
+  </si>
+  <si>
+    <t>R-48</t>
+  </si>
+  <si>
+    <t>L-50</t>
+  </si>
+  <si>
+    <t>R-49</t>
+  </si>
+  <si>
+    <t>L-51</t>
+  </si>
+  <si>
+    <t>R-50</t>
+  </si>
+  <si>
+    <t>L-52</t>
+  </si>
+  <si>
+    <t>R-51</t>
+  </si>
+  <si>
+    <t>L-53</t>
+  </si>
+  <si>
+    <t>R-52</t>
+  </si>
+  <si>
+    <t>L-54</t>
+  </si>
+  <si>
+    <t>R-53</t>
+  </si>
+  <si>
+    <t>L-55</t>
+  </si>
+  <si>
+    <t>R-54</t>
+  </si>
+  <si>
+    <t>L-56</t>
+  </si>
+  <si>
+    <t>R-55</t>
+  </si>
+  <si>
+    <t>L-57</t>
+  </si>
+  <si>
+    <t>R-56</t>
+  </si>
+  <si>
+    <t>L-58</t>
+  </si>
+  <si>
+    <t>R-57</t>
+  </si>
+  <si>
+    <t>L-59</t>
+  </si>
+  <si>
+    <t>R-58</t>
+  </si>
+  <si>
+    <t>R-59</t>
+  </si>
+  <si>
+    <t>R-60</t>
+  </si>
+  <si>
+    <t>R-61</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>L-60</t>
+  </si>
+  <si>
+    <t>R-62</t>
+  </si>
+  <si>
+    <t>L-61</t>
+  </si>
+  <si>
+    <t>R-63</t>
+  </si>
+  <si>
+    <t>L-62</t>
+  </si>
+  <si>
+    <t>R-64</t>
+  </si>
+  <si>
+    <t>L-63</t>
+  </si>
+  <si>
+    <t>R-65</t>
+  </si>
+  <si>
+    <t>L-64</t>
+  </si>
+  <si>
+    <t>R-66</t>
+  </si>
+  <si>
+    <t>L-65</t>
+  </si>
+  <si>
+    <t>R-67</t>
+  </si>
+  <si>
+    <t>L-66</t>
+  </si>
+  <si>
+    <t>R-68</t>
+  </si>
+  <si>
+    <t>L-67</t>
+  </si>
+  <si>
+    <t>R-69</t>
+  </si>
+  <si>
+    <t>L-68</t>
+  </si>
+  <si>
+    <t>R-70</t>
+  </si>
+  <si>
+    <t>L-69</t>
+  </si>
+  <si>
+    <t>R-71</t>
+  </si>
+  <si>
+    <t>L-70</t>
+  </si>
+  <si>
+    <t>R-72</t>
+  </si>
+  <si>
+    <t>L-71</t>
+  </si>
+  <si>
+    <t>R-73</t>
+  </si>
+  <si>
+    <t>L-72</t>
+  </si>
+  <si>
+    <t>R-74</t>
+  </si>
+  <si>
+    <t>L-73</t>
+  </si>
+  <si>
+    <t>R-75</t>
+  </si>
+  <si>
+    <t>L-74</t>
+  </si>
+  <si>
+    <t>R-76</t>
+  </si>
+  <si>
+    <t>L-75</t>
+  </si>
+  <si>
+    <t>R-77</t>
+  </si>
+  <si>
+    <t>L-76</t>
+  </si>
+  <si>
+    <t>R-78</t>
+  </si>
+  <si>
+    <t>L-77</t>
+  </si>
+  <si>
+    <t>R-79</t>
+  </si>
+  <si>
+    <t>L-78</t>
+  </si>
+  <si>
+    <t>R-80</t>
+  </si>
+  <si>
+    <t>L-79</t>
+  </si>
+  <si>
+    <t>R-81</t>
+  </si>
+  <si>
+    <t>L-80</t>
+  </si>
+  <si>
+    <t>R-82</t>
+  </si>
+  <si>
+    <t>L-81</t>
+  </si>
+  <si>
+    <t>R-83</t>
+  </si>
+  <si>
+    <t>L-82</t>
+  </si>
+  <si>
+    <t>R-84</t>
+  </si>
+  <si>
+    <t>L-83</t>
+  </si>
+  <si>
+    <t>R-85</t>
+  </si>
+  <si>
+    <t>L-84</t>
+  </si>
+  <si>
+    <t>R-86</t>
+  </si>
+  <si>
+    <t>L-85</t>
+  </si>
+  <si>
+    <t>R-87</t>
+  </si>
+  <si>
+    <t>L-86</t>
+  </si>
+  <si>
+    <t>L-87</t>
+  </si>
+  <si>
+    <t>L-88</t>
+  </si>
+  <si>
+    <t>L-89</t>
+  </si>
+  <si>
+    <t>L-90</t>
+  </si>
+  <si>
+    <t>L-91</t>
+  </si>
+  <si>
+    <t>R-X</t>
+  </si>
+  <si>
+    <t>R-Y</t>
+  </si>
+  <si>
+    <t>L-X</t>
+  </si>
+  <si>
+    <t>L-Y</t>
+  </si>
+  <si>
+    <t>-133861. 011</t>
+  </si>
+  <si>
+    <t>-76,550.559</t>
+  </si>
+  <si>
+    <t>L47</t>
+  </si>
+  <si>
+    <t>-133,815.954</t>
+  </si>
+  <si>
+    <t>-76,496.045</t>
+  </si>
+  <si>
+    <t>858.905</t>
+  </si>
+  <si>
+    <t>532.457</t>
+  </si>
+  <si>
+    <t>805.491</t>
+  </si>
+  <si>
+    <t>475.247</t>
+  </si>
+  <si>
+    <t>871.034</t>
+  </si>
+  <si>
+    <t>521.988</t>
+  </si>
+  <si>
+    <t>799.657</t>
+  </si>
+  <si>
+    <t>459.397</t>
+  </si>
+  <si>
+    <t>877. 043</t>
+  </si>
+  <si>
+    <t>497.803</t>
+  </si>
+  <si>
+    <t>795.177</t>
+  </si>
+  <si>
+    <t>443.411</t>
+  </si>
+  <si>
+    <t>855.813</t>
+  </si>
+  <si>
+    <t>505. 027</t>
+  </si>
+  <si>
+    <t>786. 424</t>
+  </si>
+  <si>
+    <t>424. 618</t>
+  </si>
+  <si>
+    <t>853. 852</t>
+  </si>
+  <si>
+    <t>465.534</t>
+  </si>
+  <si>
+    <t>774.230</t>
+  </si>
+  <si>
+    <t>393. 719</t>
+  </si>
+  <si>
+    <t>858.877</t>
+  </si>
+  <si>
+    <t>430.736</t>
+  </si>
+  <si>
+    <t>764.936</t>
+  </si>
+  <si>
+    <t>361. 981</t>
+  </si>
+  <si>
+    <t>848.385</t>
+  </si>
+  <si>
+    <t>387.503</t>
+  </si>
+  <si>
+    <t>750.409</t>
+  </si>
+  <si>
+    <t>329.621</t>
+  </si>
+  <si>
+    <t>841.416</t>
+  </si>
+  <si>
+    <t>350.999</t>
+  </si>
+  <si>
+    <t>732.225</t>
+  </si>
+  <si>
+    <t>307.371</t>
+  </si>
+  <si>
+    <t>R55</t>
+  </si>
+  <si>
+    <t>834. 589</t>
+  </si>
+  <si>
+    <t>344.606</t>
+  </si>
+  <si>
+    <t>723.940</t>
+  </si>
+  <si>
+    <t>288. 477</t>
+  </si>
+  <si>
+    <t>821. 032</t>
+  </si>
+  <si>
+    <t>335. 823</t>
+  </si>
+  <si>
+    <t>710. 435</t>
+  </si>
+  <si>
+    <t>272. 314</t>
+  </si>
+  <si>
+    <t>797. 230</t>
+  </si>
+  <si>
+    <t>351. 190</t>
+  </si>
+  <si>
+    <t>702. 553</t>
+  </si>
+  <si>
+    <t>259. 974</t>
+  </si>
+  <si>
+    <t>791.923</t>
+  </si>
+  <si>
+    <t>333.037</t>
+  </si>
+  <si>
+    <t>-133,697.620</t>
+  </si>
+  <si>
+    <t>-76,243.016</t>
+  </si>
+  <si>
+    <t>771.921</t>
+  </si>
+  <si>
+    <t>302.770</t>
+  </si>
+  <si>
+    <t>746.855</t>
+  </si>
+  <si>
+    <t>271.465</t>
+  </si>
+  <si>
+    <t>-133, 734. 537</t>
+  </si>
+  <si>
+    <t>-76243.852</t>
+  </si>
+  <si>
+    <t>Unnamed: 0</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>R-X(復元)</t>
+  </si>
+  <si>
+    <t>R-Y(復元)</t>
+  </si>
+  <si>
+    <t>L-X(復元)</t>
+  </si>
+  <si>
+    <t>L-Y(復元)</t>
   </si>
 </sst>
 </file>
@@ -466,7 +856,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.000_ "/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,6 +876,13 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -495,7 +892,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -503,15 +900,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -825,9 +1240,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85E9FCA5-FE9D-AF4B-8B27-F7A4FA722402}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L85"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -840,51 +1255,51 @@
     <col min="11" max="11" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.6640625" style="1" customWidth="1"/>
     <col min="13" max="14" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="10.83203125" style="1"/>
+    <col min="15" max="26" width="10.83203125" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="19">
+    <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>115</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>114</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="2"/>
+        <v>5</v>
+      </c>
       <c r="H1" s="1" t="s">
-        <v>111</v>
+        <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2">
         <v>-131257.1692</v>
@@ -892,11 +1307,8 @@
       <c r="D2" s="2">
         <v>-49204.167500000003</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="H2" s="1" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="I2" s="2">
         <v>-131232.22899999999</v>
@@ -904,15 +1316,14 @@
       <c r="J2" s="2">
         <v>-49212.247000000003</v>
       </c>
-      <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="19">
+    <row r="3" spans="1:12">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2">
         <v>-131288.89000000001</v>
@@ -920,11 +1331,8 @@
       <c r="D3" s="2">
         <v>-49247.114999999998</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="I3" s="2">
         <v>-131268.74600000001</v>
@@ -932,15 +1340,14 @@
       <c r="J3" s="2">
         <v>-49261.923000000003</v>
       </c>
-      <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="19">
+    <row r="4" spans="1:12">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2">
         <v>-131324.427</v>
@@ -948,11 +1355,8 @@
       <c r="D4" s="2">
         <v>-49295.457999999999</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I4" s="2">
         <v>-131304.28400000001</v>
@@ -960,14 +1364,13 @@
       <c r="J4" s="2">
         <v>-49310.266000000003</v>
       </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2">
         <v>-131358.32999999999</v>
@@ -975,11 +1378,8 @@
       <c r="D5" s="2">
         <v>-49341.578000000001</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2">
         <v>-131338.18599999999</v>
@@ -987,14 +1387,13 @@
       <c r="J5" s="2">
         <v>-49356.385000000002</v>
       </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2">
         <v>-131365.14199999999</v>
@@ -1002,11 +1401,8 @@
       <c r="D6" s="2">
         <v>-49350.790999999997</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I6" s="2">
         <v>-131345.10200000001</v>
@@ -1014,14 +1410,13 @@
       <c r="J6" s="2">
         <v>-49365.78</v>
       </c>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2">
         <v>-131371.99900000001</v>
@@ -1029,11 +1424,8 @@
       <c r="D7" s="2">
         <v>-49359.752</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I7" s="2">
         <v>-131352.054</v>
@@ -1041,14 +1433,13 @@
       <c r="J7" s="2">
         <v>-49375.15</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2">
         <v>-131379.01800000001</v>
@@ -1056,11 +1447,8 @@
       <c r="D8" s="2">
         <v>-49368.319000000003</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
       <c r="H8" s="1" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="I8" s="2">
         <v>-131359.97500000001</v>
@@ -1068,15 +1456,14 @@
       <c r="J8" s="2">
         <v>-49384.641000000003</v>
       </c>
-      <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" ht="19">
+    <row r="9" spans="1:12">
       <c r="A9" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2">
         <v>-131386.35699999999</v>
@@ -1084,11 +1471,8 @@
       <c r="D9" s="2">
         <v>-49376.411</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
       <c r="H9" s="1" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="I9" s="2">
         <v>-131368.25099999999</v>
@@ -1096,14 +1480,13 @@
       <c r="J9" s="2">
         <v>-49393.78</v>
       </c>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2">
         <v>-131394.10500000001</v>
@@ -1111,9 +1494,6 @@
       <c r="D10" s="2">
         <v>-49384.033000000003</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
       <c r="H10" s="1" t="s">
         <v>29</v>
       </c>
@@ -1123,15 +1503,14 @@
       <c r="J10" s="2">
         <v>-49402.421000000002</v>
       </c>
-      <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" s="1" customFormat="1" ht="19">
+    <row r="11" spans="1:12">
       <c r="A11" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2">
         <v>-131402.28200000001</v>
@@ -1139,11 +1518,8 @@
       <c r="D11" s="2">
         <v>-49391.207000000002</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
       <c r="H11" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I11" s="2">
         <v>-131386.31200000001</v>
@@ -1151,14 +1527,13 @@
       <c r="J11" s="2">
         <v>-49410.474000000002</v>
       </c>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2">
         <v>-131410.96400000001</v>
@@ -1166,11 +1541,8 @@
       <c r="D12" s="2">
         <v>-49398.082999999999</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
       <c r="H12" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I12" s="2">
         <v>-131395.79199999999</v>
@@ -1178,14 +1550,13 @@
       <c r="J12" s="2">
         <v>-49418.016000000003</v>
       </c>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2">
         <v>-131420.03599999999</v>
@@ -1193,11 +1564,8 @@
       <c r="D13" s="2">
         <v>-49404.792000000001</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
       <c r="H13" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I13" s="2">
         <v>-131405.34700000001</v>
@@ -1205,14 +1573,13 @@
       <c r="J13" s="2">
         <v>-49425.120999999999</v>
       </c>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2">
         <v>-131429.38699999999</v>
@@ -1220,11 +1587,8 @@
       <c r="D14" s="2">
         <v>-49411.470999999998</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
       <c r="H14" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I14" s="2">
         <v>-131414.91500000001</v>
@@ -1232,14 +1596,13 @@
       <c r="J14" s="2">
         <v>-49431.855000000003</v>
       </c>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C15" s="2">
         <v>-131430.644</v>
@@ -1247,11 +1610,8 @@
       <c r="D15" s="2">
         <v>-49412.364000000001</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
       <c r="H15" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I15" s="2">
         <v>-131416.17199999999</v>
@@ -1259,14 +1619,13 @@
       <c r="J15" s="2">
         <v>-49432.748</v>
       </c>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C16" s="2">
         <v>-131438.36199999999</v>
@@ -1274,11 +1633,8 @@
       <c r="D16" s="2">
         <v>-49417.86</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
       <c r="H16" s="1" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="I16" s="2">
         <v>-131423.72399999999</v>
@@ -1286,14 +1642,13 @@
       <c r="J16" s="2">
         <v>-49438.139000000003</v>
       </c>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" ht="19">
+    </row>
+    <row r="17" spans="1:10" s="2" customFormat="1">
       <c r="A17" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C17" s="2">
         <v>-131446.16099999999</v>
@@ -1302,7 +1657,7 @@
         <v>-49423.578000000001</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="I17" s="2">
         <v>-131431.033</v>
@@ -1311,12 +1666,12 @@
         <v>-49443.531000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="18" spans="1:10" s="2" customFormat="1">
       <c r="A18" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2">
         <v>-131453.92600000001</v>
@@ -1325,7 +1680,7 @@
         <v>-49429.665000000001</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="I18" s="2">
         <v>-131438.01800000001</v>
@@ -1334,12 +1689,12 @@
         <v>-49449.029000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="19" spans="1:10" s="2" customFormat="1">
       <c r="A19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C19" s="2">
         <v>-131461.53400000001</v>
@@ -1348,7 +1703,7 @@
         <v>-49436.24</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="I19" s="2">
         <v>-131444.59</v>
@@ -1357,12 +1712,12 @@
         <v>-49454.722000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="20" spans="1:10" s="2" customFormat="1">
       <c r="A20" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2">
         <v>-131468.785</v>
@@ -1371,7 +1726,7 @@
         <v>-49443.288999999997</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="I20" s="2">
         <v>-131450.78700000001</v>
@@ -1380,12 +1735,12 @@
         <v>-49460.747000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="21" spans="1:10" s="2" customFormat="1">
       <c r="A21" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="C21" s="2">
         <v>-131475.60999999999</v>
@@ -1394,7 +1749,7 @@
         <v>-49450.750999999997</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="I21" s="2">
         <v>-131456.62100000001</v>
@@ -1403,12 +1758,12 @@
         <v>-49467.125</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="22" spans="1:10" s="2" customFormat="1">
       <c r="A22" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="C22" s="2">
         <v>-131481.98699999999</v>
@@ -1417,7 +1772,7 @@
         <v>-49458.599000000002</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="I22" s="2">
         <v>-131462.071</v>
@@ -1426,12 +1781,12 @@
         <v>-49473.832999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="23" spans="1:10" s="2" customFormat="1">
       <c r="A23" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C23" s="2">
         <v>-131487.85399999999</v>
@@ -1440,7 +1795,7 @@
         <v>-49466.754000000001</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="I23" s="2">
         <v>-131467.15100000001</v>
@@ -1449,12 +1804,12 @@
         <v>-49480.875</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="24" spans="1:10" s="2" customFormat="1">
       <c r="A24" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="C24" s="2">
         <v>-131493.22700000001</v>
@@ -1463,7 +1818,7 @@
         <v>-49475.03</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="I24" s="2">
         <v>-131472.005</v>
@@ -1472,12 +1827,12 @@
         <v>-49488.321000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="25" spans="1:10" s="2" customFormat="1">
       <c r="A25" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2">
         <v>-131498.228</v>
@@ -1486,7 +1841,7 @@
         <v>-49483.307000000001</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="I25" s="2">
         <v>-131476.72700000001</v>
@@ -1495,12 +1850,12 @@
         <v>-49496.082000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="26" spans="1:10" s="2" customFormat="1">
       <c r="A26" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="C26" s="2">
         <v>-131503.016</v>
@@ -1509,7 +1864,7 @@
         <v>-49491.482000000004</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="I26" s="2">
         <v>-131481.424</v>
@@ -1518,12 +1873,12 @@
         <v>-49504.084000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="27" spans="1:10" s="2" customFormat="1">
       <c r="A27" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2">
         <v>-131530.51800000001</v>
@@ -1532,7 +1887,7 @@
         <v>-49538.605000000003</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="I27" s="2">
         <v>-131508.92600000001</v>
@@ -1541,12 +1896,12 @@
         <v>-49551.205999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="28" spans="1:10" s="2" customFormat="1">
       <c r="A28" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="C28" s="2">
         <v>-131533.24799999999</v>
@@ -1555,7 +1910,7 @@
         <v>-49543.184000000001</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I28" s="2">
         <v>-131511.83100000001</v>
@@ -1564,12 +1919,12 @@
         <v>-49556.220999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="29" spans="1:10" s="2" customFormat="1">
       <c r="A29" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="C29" s="2">
         <v>-131539.95499999999</v>
@@ -1578,7 +1933,7 @@
         <v>-49553.682999999997</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="I29" s="2">
         <v>-131519.122</v>
@@ -1587,12 +1942,12 @@
         <v>-49567.633999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="1" customFormat="1" ht="19">
+    <row r="30" spans="1:10">
       <c r="A30" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="C30" s="2">
         <v>-131547.10999999999</v>
@@ -1600,11 +1955,8 @@
       <c r="D30" s="2">
         <v>-49563.88</v>
       </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
       <c r="H30" s="1" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="I30" s="2">
         <v>-131526.902</v>
@@ -1612,14 +1964,13 @@
       <c r="J30" s="2">
         <v>-49578.722000000002</v>
       </c>
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:11" s="2" customFormat="1" ht="19">
+    </row>
+    <row r="31" spans="1:10" s="2" customFormat="1">
       <c r="A31" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2">
         <v>-131554.701</v>
@@ -1628,7 +1979,7 @@
         <v>-49573.758999999998</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="I31" s="2">
         <v>-131535.155</v>
@@ -1637,12 +1988,12 @@
         <v>-49589.463000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="2" customFormat="1" ht="19">
+    <row r="32" spans="1:10" s="2" customFormat="1">
       <c r="A32" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2">
         <v>-131562.712</v>
@@ -1651,7 +2002,7 @@
         <v>-49583.3</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I32" s="2">
         <v>-131543.86499999999</v>
@@ -1660,12 +2011,12 @@
         <v>-49599.836000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="33" spans="1:10" s="2" customFormat="1">
       <c r="A33" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C33" s="2">
         <v>-131571.13</v>
@@ -1674,7 +2025,7 @@
         <v>-49592.483999999997</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I33" s="2">
         <v>-131553.016</v>
@@ -1683,12 +2034,12 @@
         <v>-49609.82</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="34" spans="1:10" s="2" customFormat="1">
       <c r="A34" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C34" s="2">
         <v>-131579.93700000001</v>
@@ -1697,7 +2048,7 @@
         <v>-49601.294999999998</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I34" s="2">
         <v>-131562.592</v>
@@ -1706,12 +2057,12 @@
         <v>-49619.4</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="35" spans="1:10" s="2" customFormat="1">
       <c r="A35" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C35" s="2">
         <v>-131583.82</v>
@@ -1720,7 +2071,7 @@
         <v>-49604.947</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I35" s="2">
         <v>-131566.86300000001</v>
@@ -1729,12 +2080,12 @@
         <v>-49623.317000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="36" spans="1:10" s="2" customFormat="1">
       <c r="A36" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C36" s="2">
         <v>-131620.54999999999</v>
@@ -1743,7 +2094,7 @@
         <v>-49638.851000000002</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I36" s="2">
         <v>-131603.59299999999</v>
@@ -1752,12 +2103,12 @@
         <v>-49657.220999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="37" spans="1:10" s="2" customFormat="1">
       <c r="A37" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C37" s="2">
         <v>-131657.29</v>
@@ -1766,7 +2117,7 @@
         <v>-49672.764999999999</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I37" s="2">
         <v>-131640.33300000001</v>
@@ -1775,12 +2126,12 @@
         <v>-49691.133999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="38" spans="1:10" s="2" customFormat="1">
       <c r="A38" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C38" s="2">
         <v>-131700.973</v>
@@ -1789,7 +2140,7 @@
         <v>-49713.084999999999</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="I38" s="2">
         <v>-131709.427</v>
@@ -1798,12 +2149,12 @@
         <v>-49757.21</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="39" spans="1:10" s="2" customFormat="1">
       <c r="A39" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C39" s="2">
         <v>-131706.552</v>
@@ -1812,7 +2163,7 @@
         <v>-49718.231</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I39" s="2">
         <v>-131718.935</v>
@@ -1821,12 +2172,12 @@
         <v>-49768.197999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="40" spans="1:10" s="2" customFormat="1">
       <c r="A40" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C40" s="2">
         <v>-131717.52299999999</v>
@@ -1835,7 +2186,7 @@
         <v>-49729.14</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="I40" s="2">
         <v>-131728.02299999999</v>
@@ -1844,12 +2195,12 @@
         <v>-49779.536</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="41" spans="1:10" s="2" customFormat="1">
       <c r="A41" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C41" s="2">
         <v>-131728.07699999999</v>
@@ -1858,7 +2209,7 @@
         <v>-49740.453000000001</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="I41" s="2">
         <v>-131736.68</v>
@@ -1867,12 +2218,12 @@
         <v>-49791.207000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="42" spans="1:10" s="2" customFormat="1">
       <c r="A42" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="C42" s="2">
         <v>-131738.20000000001</v>
@@ -1881,7 +2232,7 @@
         <v>-49752.152999999998</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="I42" s="2">
         <v>-131744.894</v>
@@ -1890,12 +2241,12 @@
         <v>-49803.194000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="43" spans="1:10" s="2" customFormat="1">
       <c r="A43" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="C43" s="2">
         <v>-131747.87599999999</v>
@@ -1904,7 +2255,7 @@
         <v>-49764.224000000002</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="I43" s="2">
         <v>-131752.65299999999</v>
@@ -1913,12 +2264,12 @@
         <v>-49815.48</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="44" spans="1:10" s="2" customFormat="1">
       <c r="A44" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="C44" s="2">
         <v>-131757.09400000001</v>
@@ -1927,7 +2278,7 @@
         <v>-49776.65</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="I44" s="2">
         <v>-131759.94500000001</v>
@@ -1936,12 +2287,12 @@
         <v>-49828.048999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="45" spans="1:10" s="2" customFormat="1">
       <c r="A45" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="C45" s="2">
         <v>-131760.82999999999</v>
@@ -1950,7 +2301,7 @@
         <v>-49782.101999999999</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="I45" s="2">
         <v>-131763.35</v>
@@ -1959,12 +2310,12 @@
         <v>-49834.313999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="46" spans="1:10" s="2" customFormat="1">
       <c r="A46" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="C46" s="2">
         <v>-131762.82800000001</v>
@@ -1973,7 +2324,7 @@
         <v>-49784.192000000003</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="I46" s="2">
         <v>-131789.53899999999</v>
@@ -1982,12 +2333,12 @@
         <v>-49883.588000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="47" spans="1:10" s="2" customFormat="1">
       <c r="A47" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2">
         <v>-131768.07199999999</v>
@@ -1996,7 +2347,7 @@
         <v>-49792.95</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="I47" s="2">
         <v>-131813.00700000001</v>
@@ -2005,12 +2356,12 @@
         <v>-49927.737000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:10" s="2" customFormat="1" ht="19">
+    <row r="48" spans="1:10" s="2" customFormat="1">
       <c r="A48" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="C48" s="2">
         <v>-131774.09899999999</v>
@@ -2019,7 +2370,7 @@
         <v>-49802.493999999999</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="I48" s="2">
         <v>-131836.47399999999</v>
@@ -2028,12 +2379,12 @@
         <v>-49971.887000000002</v>
       </c>
     </row>
-    <row r="49" spans="1:12" s="2" customFormat="1" ht="19">
+    <row r="49" spans="1:12" s="2" customFormat="1">
       <c r="A49" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="C49" s="2">
         <v>-131781.86300000001</v>
@@ -2044,12 +2395,12 @@
       <c r="H49" s="1"/>
       <c r="L49" s="1"/>
     </row>
-    <row r="50" spans="1:12" s="2" customFormat="1" ht="19">
+    <row r="50" spans="1:12" s="2" customFormat="1">
       <c r="A50" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="C50" s="2">
         <v>-131782.36900000001</v>
@@ -2060,12 +2411,12 @@
       <c r="H50" s="1"/>
       <c r="L50" s="1"/>
     </row>
-    <row r="51" spans="1:12" s="2" customFormat="1" ht="19">
+    <row r="51" spans="1:12" s="2" customFormat="1">
       <c r="A51" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="C51" s="2">
         <v>-131789.83499999999</v>
@@ -2076,12 +2427,12 @@
       <c r="H51" s="1"/>
       <c r="L51" s="1"/>
     </row>
-    <row r="52" spans="1:12" s="2" customFormat="1" ht="19">
+    <row r="52" spans="1:12" s="2" customFormat="1">
       <c r="A52" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="C52" s="2">
         <v>-131811.92300000001</v>
@@ -2092,12 +2443,12 @@
       <c r="H52" s="1"/>
       <c r="L52" s="1"/>
     </row>
-    <row r="53" spans="1:12" s="1" customFormat="1" ht="19">
+    <row r="53" spans="1:12">
       <c r="A53" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="C53" s="2">
         <v>-131831.23000000001</v>
@@ -2105,19 +2456,13 @@
       <c r="D53" s="2">
         <v>-49908.752999999997</v>
       </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="C54" s="2">
         <v>-131858.54999999999</v>
@@ -2125,19 +2470,13 @@
       <c r="D54" s="2">
         <v>-49960.152999999998</v>
       </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="56" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C56" s="2">
         <v>-131858.54999999999</v>
@@ -2145,11 +2484,8 @@
       <c r="D56" s="2">
         <v>-49960.152999999998</v>
       </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
       <c r="H56" s="1" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="I56" s="2">
         <v>-131836.47399999999</v>
@@ -2157,14 +2493,13 @@
       <c r="J56" s="2">
         <v>-49971.887000000002</v>
       </c>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C57" s="2">
         <v>-131882.01800000001</v>
@@ -2172,11 +2507,8 @@
       <c r="D57" s="2">
         <v>-50004.123</v>
       </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
       <c r="H57" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="I57" s="2">
         <v>-131859.94200000001</v>
@@ -2184,14 +2516,13 @@
       <c r="J57" s="2">
         <v>-50016.036999999997</v>
       </c>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C58" s="2">
         <v>-131902.74400000001</v>
@@ -2199,11 +2530,8 @@
       <c r="D58" s="2">
         <v>-50043.294000000002</v>
       </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
       <c r="H58" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I58" s="2">
         <v>-131880.625</v>
@@ -2211,14 +2539,13 @@
       <c r="J58" s="2">
         <v>-50054.947999999997</v>
       </c>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C59" s="2">
         <v>-131910.046</v>
@@ -2226,11 +2553,8 @@
       <c r="D59" s="2">
         <v>-50056.830999999998</v>
       </c>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
       <c r="H59" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I59" s="2">
         <v>-131897.09099999999</v>
@@ -2238,14 +2562,13 @@
       <c r="J59" s="2">
         <v>-50085.798000000003</v>
       </c>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C60" s="2">
         <v>-131939.08900000001</v>
@@ -2253,11 +2576,8 @@
       <c r="D60" s="2">
         <v>-50110.669000000002</v>
       </c>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
       <c r="H60" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I60" s="2">
         <v>-131919.90100000001</v>
@@ -2265,14 +2585,13 @@
       <c r="J60" s="2">
         <v>-50128.076999999997</v>
       </c>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C61" s="2">
         <v>-131943.28400000001</v>
@@ -2280,11 +2599,8 @@
       <c r="D61" s="2">
         <v>-50118.446000000004</v>
       </c>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
       <c r="H61" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I61" s="2">
         <v>-131930.611</v>
@@ -2292,17 +2608,16 @@
       <c r="J61" s="2">
         <v>-50157.696000000004</v>
       </c>
-      <c r="K61" s="2"/>
       <c r="L61" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" s="1" customFormat="1" ht="19">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C62" s="2">
         <v>-131951.53099999999</v>
@@ -2310,19 +2625,13 @@
       <c r="D62" s="2">
         <v>-50130.817000000003</v>
       </c>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C63" s="2">
         <v>-131955.62299999999</v>
@@ -2330,19 +2639,13 @@
       <c r="D63" s="2">
         <v>-50144.383000000002</v>
       </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-    </row>
-    <row r="64" spans="1:12" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C64" s="2">
         <v>-131956.503</v>
@@ -2350,9 +2653,6 @@
       <c r="D64" s="2">
         <v>-50146.49</v>
       </c>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
       <c r="H64" s="1" t="s">
         <v>29</v>
       </c>
@@ -2362,17 +2662,16 @@
       <c r="J64" s="2">
         <v>-50197.455999999998</v>
       </c>
-      <c r="K64" s="2"/>
       <c r="L64" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" s="1" customFormat="1" ht="19">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C65" s="2">
         <v>-131959.899</v>
@@ -2380,11 +2679,8 @@
       <c r="D65" s="2">
         <v>-50156.226999999999</v>
       </c>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
       <c r="H65" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I65" s="2">
         <v>-131950.26999999999</v>
@@ -2392,14 +2688,13 @@
       <c r="J65" s="2">
         <v>-50260.33</v>
       </c>
-      <c r="K65" s="2"/>
-    </row>
-    <row r="66" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C66" s="2">
         <v>-131962.70800000001</v>
@@ -2407,11 +2702,8 @@
       <c r="D66" s="2">
         <v>-50166.148999999998</v>
       </c>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
       <c r="H66" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I66" s="2">
         <v>-131947.85699999999</v>
@@ -2419,14 +2711,13 @@
       <c r="J66" s="2">
         <v>-50258.514000000003</v>
       </c>
-      <c r="K66" s="2"/>
-    </row>
-    <row r="67" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C67" s="2">
         <v>-131963.29399999999</v>
@@ -2434,11 +2725,8 @@
       <c r="D67" s="2">
         <v>-50168.822999999997</v>
       </c>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
       <c r="H67" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I67" s="2">
         <v>-131953.80499999999</v>
@@ -2446,14 +2734,13 @@
       <c r="J67" s="2">
         <v>-50308.158000000003</v>
       </c>
-      <c r="K67" s="2"/>
-    </row>
-    <row r="68" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C68" s="2">
         <v>-131966.41200000001</v>
@@ -2461,11 +2748,8 @@
       <c r="D68" s="2">
         <v>-50178.356</v>
       </c>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
       <c r="H68" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I68" s="2">
         <v>-131959.73800000001</v>
@@ -2473,14 +2757,13 @@
       <c r="J68" s="2">
         <v>-50357.803999999996</v>
       </c>
-      <c r="K68" s="2"/>
-    </row>
-    <row r="69" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C69" s="2">
         <v>-131967.432</v>
@@ -2488,11 +2771,8 @@
       <c r="D69" s="2">
         <v>-50184.525000000001</v>
       </c>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
       <c r="H69" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I69" s="2">
         <v>-131966.95499999999</v>
@@ -2500,14 +2780,13 @@
       <c r="J69" s="2">
         <v>-50417.11</v>
       </c>
-      <c r="K69" s="2"/>
-    </row>
-    <row r="70" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C70" s="2">
         <v>-131977.92199999999</v>
@@ -2515,11 +2794,8 @@
       <c r="D70" s="2">
         <v>-50231.953999999998</v>
       </c>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
       <c r="H70" s="1" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="I70" s="2">
         <v>-131974.82999999999</v>
@@ -2527,14 +2803,13 @@
       <c r="J70" s="2">
         <v>-50484.396000000001</v>
       </c>
-      <c r="K70" s="2"/>
-    </row>
-    <row r="71" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C71" s="2">
         <v>-131971.35800000001</v>
@@ -2542,19 +2817,13 @@
       <c r="D71" s="2">
         <v>-50225.499000000003</v>
       </c>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-    </row>
-    <row r="72" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C72" s="2">
         <v>-131977.88200000001</v>
@@ -2562,19 +2831,13 @@
       <c r="D72" s="2">
         <v>-50281.103000000003</v>
       </c>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-    </row>
-    <row r="73" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C73" s="2">
         <v>-131983.03400000001</v>
@@ -2582,19 +2845,13 @@
       <c r="D73" s="2">
         <v>-50284.966999999997</v>
       </c>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-    </row>
-    <row r="74" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C74" s="2">
         <v>-131985.408</v>
@@ -2602,19 +2859,13 @@
       <c r="D74" s="2">
         <v>-50307.38</v>
       </c>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-    </row>
-    <row r="75" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="C75" s="2">
         <v>-131987.595</v>
@@ -2622,19 +2873,13 @@
       <c r="D75" s="2">
         <v>-50324.673000000003</v>
       </c>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-    </row>
-    <row r="76" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="C76" s="2">
         <v>-131982.26699999999</v>
@@ -2642,19 +2887,13 @@
       <c r="D76" s="2">
         <v>-50318.533000000003</v>
       </c>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-    </row>
-    <row r="77" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C77" s="2">
         <v>-131986.89600000001</v>
@@ -2662,19 +2901,13 @@
       <c r="D77" s="2">
         <v>-50358.012999999999</v>
       </c>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-    </row>
-    <row r="78" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="C78" s="2">
         <v>-131991.829</v>
@@ -2682,34 +2915,21 @@
       <c r="D78" s="2">
         <v>-50400.082999999999</v>
       </c>
-      <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-    </row>
-    <row r="79" spans="1:11" s="1" customFormat="1" ht="19">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-    </row>
-    <row r="80" spans="1:11" s="1" customFormat="1" ht="19">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="C80" s="2">
         <v>-131994.69200000001</v>
@@ -2717,21 +2937,16 @@
       <c r="D80" s="2">
         <v>-50422.785000000003</v>
       </c>
-      <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="1:11" s="1" customFormat="1" ht="19">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="C81" s="2">
         <v>-131999.68299999999</v>
@@ -2739,19 +2954,13 @@
       <c r="D81" s="2">
         <v>-50464.749000000003</v>
       </c>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-    </row>
-    <row r="82" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="C82" s="2">
         <v>-132006.98300000001</v>
@@ -2759,19 +2968,13 @@
       <c r="D82" s="2">
         <v>-50493.148999999998</v>
       </c>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-    </row>
-    <row r="83" spans="1:11" s="1" customFormat="1" ht="19">
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="C83" s="2">
         <v>-132020.48300000001</v>
@@ -2779,34 +2982,21 @@
       <c r="D83" s="2">
         <v>-50515.847999999998</v>
       </c>
-      <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
-    </row>
-    <row r="84" spans="1:11" s="1" customFormat="1" ht="19">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-    </row>
-    <row r="85" spans="1:11" s="1" customFormat="1" ht="19">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="C85" s="2">
         <v>-132012.74600000001</v>
@@ -2814,14 +3004,9 @@
       <c r="D85" s="2">
         <v>-50529.622000000003</v>
       </c>
-      <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2"/>
+        <v>115</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -2831,7 +3016,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCAA128-AB91-ED49-AB23-358535EAEAFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19"/>
   <cols>
@@ -2846,51 +3031,51 @@
     <col min="11" max="11" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.6640625" style="1" customWidth="1"/>
     <col min="13" max="14" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="10.83203125" style="1"/>
+    <col min="15" max="26" width="10.83203125" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>115</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>114</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="2"/>
+        <v>5</v>
+      </c>
       <c r="H1" s="1" t="s">
-        <v>111</v>
+        <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2">
         <v>-119546.681</v>
@@ -2898,11 +3083,8 @@
       <c r="D2" s="2">
         <v>-55164.877999999997</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="H2" s="1" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="I2" s="2">
         <v>-119576.03200000001</v>
@@ -2910,15 +3092,14 @@
       <c r="J2" s="2">
         <v>-55163.389000000003</v>
       </c>
-      <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" spans="1:12">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2">
         <v>-119548.359</v>
@@ -2926,11 +3107,8 @@
       <c r="D3" s="2">
         <v>-55163.788999999997</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="I3" s="2">
         <v>-119571.948</v>
@@ -2938,15 +3116,14 @@
       <c r="J3" s="2">
         <v>-55157.097999999998</v>
       </c>
-      <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1">
+    <row r="4" spans="1:12">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2">
         <v>-119574.33100000001</v>
@@ -2954,11 +3131,8 @@
       <c r="D4" s="2">
         <v>-55112.671000000002</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I4" s="2">
         <v>-119590.38099999999</v>
@@ -2966,14 +3140,13 @@
       <c r="J4" s="2">
         <v>-55120.819000000003</v>
       </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2">
         <v>-119572.78</v>
@@ -2981,11 +3154,8 @@
       <c r="D5" s="2">
         <v>-55107.917999999998</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2">
         <v>-119595.13400000001</v>
@@ -2993,14 +3163,13 @@
       <c r="J5" s="2">
         <v>-55119.267999999996</v>
       </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2">
         <v>-119579.575</v>
@@ -3008,11 +3177,8 @@
       <c r="D6" s="2">
         <v>-55094.544999999998</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I6" s="2">
         <v>-119601.929</v>
@@ -3020,14 +3186,13 @@
       <c r="J6" s="2">
         <v>-55105.896000000001</v>
       </c>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2">
         <v>-119584.32799999999</v>
@@ -3035,11 +3200,8 @@
       <c r="D7" s="2">
         <v>-55092.993999999999</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I7" s="2">
         <v>-119600.378</v>
@@ -3047,14 +3209,13 @@
       <c r="J7" s="2">
         <v>-55101.142</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2">
         <v>-119608.503</v>
@@ -3062,11 +3223,8 @@
       <c r="D8" s="2">
         <v>-55045.411999999997</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
       <c r="H8" s="1" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="I8" s="2">
         <v>-119624.62300000001</v>
@@ -3074,15 +3232,14 @@
       <c r="J8" s="2">
         <v>-55053.423000000003</v>
       </c>
-      <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" s="1" customFormat="1">
+    <row r="9" spans="1:12">
       <c r="A9" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2">
         <v>-119607.56200000001</v>
@@ -3090,11 +3247,8 @@
       <c r="D9" s="2">
         <v>-55042.563999999998</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
       <c r="H9" s="1" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="I9" s="2">
         <v>-119627.47100000001</v>
@@ -3102,14 +3256,13 @@
       <c r="J9" s="2">
         <v>-55052.482000000004</v>
       </c>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2">
         <v>-119611.2</v>
@@ -3117,9 +3270,6 @@
       <c r="D10" s="2">
         <v>-55035.438999999998</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
       <c r="H10" s="1" t="s">
         <v>29</v>
       </c>
@@ -3129,15 +3279,14 @@
       <c r="J10" s="2">
         <v>-55045.357000000004</v>
       </c>
-      <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" s="1" customFormat="1">
+    <row r="11" spans="1:12">
       <c r="A11" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2">
         <v>-119614.049</v>
@@ -3145,11 +3294,8 @@
       <c r="D11" s="2">
         <v>-55034.497000000003</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
       <c r="H11" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I11" s="2">
         <v>-119630.16899999999</v>
@@ -3157,14 +3303,13 @@
       <c r="J11" s="2">
         <v>-55042.508000000002</v>
       </c>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2">
         <v>-119637.448</v>
@@ -3172,11 +3317,8 @@
       <c r="D12" s="2">
         <v>-54988.442000000003</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
       <c r="H12" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I12" s="2">
         <v>-119653.503</v>
@@ -3184,14 +3326,13 @@
       <c r="J12" s="2">
         <v>-54996.580999999998</v>
       </c>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2">
         <v>-119635.89599999999</v>
@@ -3199,11 +3340,8 @@
       <c r="D13" s="2">
         <v>-54983.688999999998</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
       <c r="H13" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I13" s="2">
         <v>-119658.25599999999</v>
@@ -3211,14 +3349,13 @@
       <c r="J13" s="2">
         <v>-54995.029000000002</v>
       </c>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2">
         <v>-119640.88099999999</v>
@@ -3226,11 +3363,8 @@
       <c r="D14" s="2">
         <v>-54973.883000000002</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
       <c r="H14" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I14" s="2">
         <v>-119663.24099999999</v>
@@ -3238,14 +3372,13 @@
       <c r="J14" s="2">
         <v>-54985.222999999998</v>
       </c>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C15" s="2">
         <v>-119645.63400000001</v>
@@ -3253,11 +3386,8 @@
       <c r="D15" s="2">
         <v>-54972.330999999998</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
       <c r="H15" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I15" s="2">
         <v>-119661.689</v>
@@ -3265,14 +3395,13 @@
       <c r="J15" s="2">
         <v>-54980.47</v>
       </c>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C16" s="2">
         <v>-119668.583</v>
@@ -3280,11 +3409,8 @@
       <c r="D16" s="2">
         <v>-54927.163</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
       <c r="H16" s="1" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="I16" s="2">
         <v>-119684.64200000001</v>
@@ -3292,14 +3418,13 @@
       <c r="J16" s="2">
         <v>-54935.292000000001</v>
       </c>
-      <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:10" s="2" customFormat="1">
       <c r="A17" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C17" s="2">
         <v>-119667.65</v>
@@ -3308,7 +3433,7 @@
         <v>-54924.311000000002</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="I17" s="2">
         <v>-119687.49400000001</v>
@@ -3319,10 +3444,10 @@
     </row>
     <row r="18" spans="1:10" s="2" customFormat="1">
       <c r="A18" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2">
         <v>-119671.277</v>
@@ -3331,7 +3456,7 @@
         <v>-54917.180999999997</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="I18" s="2">
         <v>-119691.12</v>
@@ -3342,10 +3467,10 @@
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1">
       <c r="A19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C19" s="2">
         <v>-119674.128</v>
@@ -3354,7 +3479,7 @@
         <v>-54916.248</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="I19" s="2">
         <v>-119690.18799999999</v>
@@ -3365,10 +3490,10 @@
     </row>
     <row r="20" spans="1:10" s="2" customFormat="1">
       <c r="A20" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2">
         <v>-119699.606</v>
@@ -3377,7 +3502,7 @@
         <v>-54866.101000000002</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="I20" s="2">
         <v>-119715.667</v>
@@ -3388,10 +3513,10 @@
     </row>
     <row r="21" spans="1:10" s="2" customFormat="1">
       <c r="A21" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="C21" s="2">
         <v>-119698.053</v>
@@ -3400,7 +3525,7 @@
         <v>-54861.349000000002</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="I21" s="2">
         <v>-119720.41899999999</v>
@@ -3411,10 +3536,10 @@
     </row>
     <row r="22" spans="1:10" s="2" customFormat="1">
       <c r="A22" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="C22" s="2">
         <v>-119708.039</v>
@@ -3423,7 +3548,7 @@
         <v>-54841.745999999999</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="I22" s="2">
         <v>-119763.80499999999</v>
@@ -3434,10 +3559,10 @@
     </row>
     <row r="23" spans="1:10" s="2" customFormat="1">
       <c r="A23" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C23" s="2">
         <v>-119712.79300000001</v>
@@ -3446,7 +3571,7 @@
         <v>-54840.196000000004</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="I23" s="2">
         <v>-119764.73699999999</v>
@@ -3457,10 +3582,10 @@
     </row>
     <row r="24" spans="1:10" s="2" customFormat="1">
       <c r="A24" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="C24" s="2">
         <v>-119728.857</v>
@@ -3469,7 +3594,7 @@
         <v>-54848.319000000003</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="I24" s="2">
         <v>-119771.876</v>
@@ -3480,10 +3605,10 @@
     </row>
     <row r="25" spans="1:10" s="2" customFormat="1">
       <c r="A25" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2">
         <v>-119730.40700000001</v>
@@ -3492,7 +3617,7 @@
         <v>-54853.072999999997</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="I25" s="2">
         <v>-119774.727</v>
@@ -3503,10 +3628,10 @@
     </row>
     <row r="26" spans="1:10" s="2" customFormat="1">
       <c r="A26" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="C26" s="2">
         <v>-119780.97900000001</v>
@@ -3515,7 +3640,7 @@
         <v>-54878.682000000001</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="I26" s="2">
         <v>-119841.569</v>
@@ -3526,10 +3651,10 @@
     </row>
     <row r="27" spans="1:10" s="2" customFormat="1">
       <c r="A27" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2">
         <v>-119785.73</v>
@@ -3538,7 +3663,7 @@
         <v>-54877.125</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="I27" s="2">
         <v>-119842.501</v>
@@ -3549,10 +3674,10 @@
     </row>
     <row r="28" spans="1:10" s="2" customFormat="1">
       <c r="A28" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="C28" s="2">
         <v>-119795.54399999999</v>
@@ -3561,7 +3686,7 @@
         <v>-54882.093999999997</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I28" s="2">
         <v>-119849.64</v>
@@ -3572,10 +3697,10 @@
     </row>
     <row r="29" spans="1:10" s="2" customFormat="1">
       <c r="A29" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="C29" s="2">
         <v>-119797.101</v>
@@ -3584,7 +3709,7 @@
         <v>-54886.845000000001</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="I29" s="2">
         <v>-119852.49099999999</v>
@@ -3595,10 +3720,10 @@
     </row>
     <row r="30" spans="1:10" s="2" customFormat="1">
       <c r="A30" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="C30" s="2">
         <v>-119883.93700000001</v>
@@ -3607,7 +3732,7 @@
         <v>-54930.817999999999</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="I30" s="2">
         <v>-119916.15</v>
@@ -3618,10 +3743,10 @@
     </row>
     <row r="31" spans="1:10" s="2" customFormat="1">
       <c r="A31" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2">
         <v>-119886.787</v>
@@ -3630,7 +3755,7 @@
         <v>-54929.883999999998</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="I31" s="2">
         <v>-119917.08199999999</v>
@@ -3641,10 +3766,10 @@
     </row>
     <row r="32" spans="1:10" s="2" customFormat="1">
       <c r="A32" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2">
         <v>-119893.924</v>
@@ -3653,7 +3778,7 @@
         <v>-54933.497000000003</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I32" s="2">
         <v>-119924.22</v>
@@ -3662,12 +3787,12 @@
         <v>-54978.252999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="2" customFormat="1">
+    <row r="33" spans="1:10" s="2" customFormat="1">
       <c r="A33" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C33" s="2">
         <v>-119894.859</v>
@@ -3676,7 +3801,7 @@
         <v>-54936.347999999998</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I33" s="2">
         <v>-119927.072</v>
@@ -3685,12 +3810,12 @@
         <v>-54977.32</v>
       </c>
     </row>
-    <row r="35" spans="1:11" s="1" customFormat="1">
+    <row r="35" spans="1:10">
       <c r="A35" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C35" s="2">
         <v>-119985.943</v>
@@ -3698,11 +3823,8 @@
       <c r="D35" s="2">
         <v>-54982.472000000002</v>
       </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
       <c r="H35" s="1" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="I35" s="2">
         <v>-119976.69100000001</v>
@@ -3710,14 +3832,13 @@
       <c r="J35" s="2">
         <v>-55002.142999999996</v>
       </c>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C36" s="2">
         <v>-119990.69500000001</v>
@@ -3725,11 +3846,8 @@
       <c r="D36" s="2">
         <v>-54980.915999999997</v>
       </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
       <c r="H36" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="I36" s="2">
         <v>-119977.667</v>
@@ -3737,14 +3855,13 @@
       <c r="J36" s="2">
         <v>-55006.887999999999</v>
       </c>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C37" s="2">
         <v>-120000.50900000001</v>
@@ -3752,11 +3869,8 @@
       <c r="D37" s="2">
         <v>-54985.883999999998</v>
       </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
       <c r="H37" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I37" s="2">
         <v>-119987.46799999999</v>
@@ -3764,14 +3878,13 @@
       <c r="J37" s="2">
         <v>-55011.883000000002</v>
       </c>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C38" s="2">
         <v>-120002.065</v>
@@ -3779,11 +3892,8 @@
       <c r="D38" s="2">
         <v>-54990.635999999999</v>
       </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
       <c r="H38" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I38" s="2">
         <v>-119992.213</v>
@@ -3791,14 +3901,13 @@
       <c r="J38" s="2">
         <v>-55010.307000000001</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C39" s="2">
         <v>-120072.50900000001</v>
@@ -3806,11 +3915,8 @@
       <c r="D39" s="2">
         <v>-55026.307999999997</v>
       </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
       <c r="H39" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I39" s="2">
         <v>-120062.567</v>
@@ -3818,14 +3924,13 @@
       <c r="J39" s="2">
         <v>-55045.932999999997</v>
       </c>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C40" s="2">
         <v>-120092.197</v>
@@ -3833,11 +3938,8 @@
       <c r="D40" s="2">
         <v>-55036.281000000003</v>
       </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
       <c r="H40" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I40" s="2">
         <v>-120064.124</v>
@@ -3845,14 +3947,13 @@
       <c r="J40" s="2">
         <v>-55050.684999999998</v>
       </c>
-      <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C41" s="2">
         <v>-120082.257</v>
@@ -3860,11 +3961,8 @@
       <c r="D41" s="2">
         <v>-55055.906999999999</v>
       </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
       <c r="H41" s="1" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="I41" s="2">
         <v>-120040.28</v>
@@ -3872,14 +3970,13 @@
       <c r="J41" s="2">
         <v>-55097.749000000003</v>
       </c>
-      <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C42" s="2">
         <v>-120077.505</v>
@@ -3887,11 +3984,8 @@
       <c r="D42" s="2">
         <v>-55057.463000000003</v>
       </c>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
       <c r="H42" s="1" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="I42" s="2">
         <v>-120037.429</v>
@@ -3899,14 +3993,13 @@
       <c r="J42" s="2">
         <v>-55098.684000000001</v>
       </c>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C43" s="2">
         <v>-120054.602</v>
@@ -3914,9 +4007,6 @@
       <c r="D43" s="2">
         <v>-55102.669000000002</v>
       </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
       <c r="H43" s="1" t="s">
         <v>29</v>
       </c>
@@ -3926,14 +4016,13 @@
       <c r="J43" s="2">
         <v>-55105.82</v>
       </c>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C44" s="2">
         <v>-120055.50199999999</v>
@@ -3941,11 +4030,8 @@
       <c r="D44" s="2">
         <v>-55105.531000000003</v>
       </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
       <c r="H44" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I44" s="2">
         <v>-120034.747</v>
@@ -3953,14 +4039,13 @@
       <c r="J44" s="2">
         <v>-55108.67</v>
       </c>
-      <c r="K44" s="2"/>
-    </row>
-    <row r="45" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C45" s="2">
         <v>-120051.93</v>
@@ -3968,11 +4053,8 @@
       <c r="D45" s="2">
         <v>-55112.692999999999</v>
       </c>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
       <c r="H45" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I45" s="2">
         <v>-120010.16</v>
@@ -3980,14 +4062,13 @@
       <c r="J45" s="2">
         <v>-55157.199000000001</v>
       </c>
-      <c r="K45" s="2"/>
-    </row>
-    <row r="46" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C46" s="2">
         <v>-120045.068</v>
@@ -3995,11 +4076,8 @@
       <c r="D46" s="2">
         <v>-55113.593000000001</v>
       </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
       <c r="H46" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I46" s="2">
         <v>-120005.409</v>
@@ -4007,14 +4085,13 @@
       <c r="J46" s="2">
         <v>-55158.754000000001</v>
       </c>
-      <c r="K46" s="2"/>
-    </row>
-    <row r="47" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C47" s="2">
         <v>-120022.84600000001</v>
@@ -4022,11 +4099,8 @@
       <c r="D47" s="2">
         <v>-55165.351000000002</v>
       </c>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
       <c r="H47" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I47" s="2">
         <v>-120000.439</v>
@@ -4034,14 +4108,13 @@
       <c r="J47" s="2">
         <v>-55168.567999999999</v>
       </c>
-      <c r="K47" s="2"/>
-    </row>
-    <row r="48" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C48" s="2">
         <v>-120023.451</v>
@@ -4049,11 +4122,8 @@
       <c r="D48" s="2">
         <v>-55167.258000000002</v>
       </c>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
       <c r="H48" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I48" s="2">
         <v>-120001.99400000001</v>
@@ -4061,14 +4131,13 @@
       <c r="J48" s="2">
         <v>-55173.32</v>
       </c>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C49" s="2">
         <v>-120020.761</v>
@@ -4076,11 +4145,8 @@
       <c r="D49" s="2">
         <v>-55172.622000000003</v>
       </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
       <c r="H49" s="1" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="I49" s="2">
         <v>-120000.03200000001</v>
@@ -4088,14 +4154,13 @@
       <c r="J49" s="2">
         <v>-55177.190999999999</v>
       </c>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C50" s="2">
         <v>-120018.855</v>
@@ -4103,11 +4168,8 @@
       <c r="D50" s="2">
         <v>-55173.228000000003</v>
       </c>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
       <c r="H50" s="1" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="I50" s="2">
         <v>-119987.322</v>
@@ -4115,14 +4177,13 @@
       <c r="J50" s="2">
         <v>-55192.733</v>
       </c>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C51" s="2">
         <v>-119977.81200000001</v>
@@ -4130,11 +4191,8 @@
       <c r="D51" s="2">
         <v>-55254.239999999998</v>
       </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
       <c r="H51" s="1" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="I51" s="2">
         <v>-119990.02800000001</v>
@@ -4142,14 +4200,13 @@
       <c r="J51" s="2">
         <v>-55196.938000000002</v>
       </c>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C52" s="2">
         <v>-119961.806</v>
@@ -4157,11 +4214,8 @@
       <c r="D52" s="2">
         <v>-55285.834999999999</v>
       </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
       <c r="H52" s="1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="I52" s="2">
         <v>-119953.31</v>
@@ -4169,14 +4223,13 @@
       <c r="J52" s="2">
         <v>-55269.411999999997</v>
       </c>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C53" s="2">
         <v>-119962.74400000001</v>
@@ -4184,11 +4237,8 @@
       <c r="D53" s="2">
         <v>-55288.684000000001</v>
       </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
       <c r="H53" s="1" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="I53" s="2">
         <v>-119950.45600000001</v>
@@ -4196,14 +4246,13 @@
       <c r="J53" s="2">
         <v>-55270.334999999999</v>
       </c>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="C54" s="2">
         <v>-119959.122</v>
@@ -4211,11 +4260,8 @@
       <c r="D54" s="2">
         <v>-55295.817999999999</v>
       </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
       <c r="H54" s="1" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="I54" s="2">
         <v>-119946.855</v>
@@ -4223,14 +4269,13 @@
       <c r="J54" s="2">
         <v>-55277.478999999999</v>
       </c>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="55" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="C55" s="2">
         <v>-119956.273</v>
@@ -4238,11 +4283,8 @@
       <c r="D55" s="2">
         <v>-55296.756000000001</v>
       </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
       <c r="H55" s="1" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="I55" s="2">
         <v>-119947.777</v>
@@ -4250,14 +4292,13 @@
       <c r="J55" s="2">
         <v>-55280.334000000003</v>
       </c>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="56" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C56" s="2">
         <v>-119927.01700000001</v>
@@ -4265,11 +4306,8 @@
       <c r="D56" s="2">
         <v>-55354.502</v>
       </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
       <c r="H56" s="1" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="I56" s="2">
         <v>-119925.715</v>
@@ -4277,19 +4315,13 @@
       <c r="J56" s="2">
         <v>-55323.881000000001</v>
       </c>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
+        <v>112</v>
+      </c>
       <c r="H57" s="1" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="I57" s="2">
         <v>-119922.863</v>
@@ -4297,19 +4329,13 @@
       <c r="J57" s="2">
         <v>-55324.811000000002</v>
       </c>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
+        <v>112</v>
+      </c>
       <c r="H58" s="1" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="I58" s="2">
         <v>-119919.25199999999</v>
@@ -4317,19 +4343,13 @@
       <c r="J58" s="2">
         <v>-55331.95</v>
       </c>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
+        <v>112</v>
+      </c>
       <c r="H59" s="1" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="I59" s="2">
         <v>-119920.162</v>
@@ -4337,19 +4357,13 @@
       <c r="J59" s="2">
         <v>-55334.802000000003</v>
       </c>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
+        <v>112</v>
+      </c>
       <c r="H60" s="1" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="I60" s="2">
         <v>-119907.79300000001</v>
@@ -4357,7 +4371,6 @@
       <c r="J60" s="2">
         <v>-55359.256999999998</v>
       </c>
-      <c r="K60" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -4367,7 +4380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27705113-C20F-0545-B6C2-385EB13167E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19"/>
   <cols>
@@ -4382,51 +4395,51 @@
     <col min="11" max="11" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.6640625" style="1" customWidth="1"/>
     <col min="13" max="14" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="10.83203125" style="1"/>
+    <col min="15" max="26" width="10.83203125" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
-      <c r="A2" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2">
         <v>-113208.516</v>
@@ -4434,11 +4447,8 @@
       <c r="D2" s="2">
         <v>-55944.135000000002</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="H2" s="1" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="I2" s="2">
         <v>-113207.238</v>
@@ -4446,15 +4456,14 @@
       <c r="J2" s="2">
         <v>-55927.404000000002</v>
       </c>
-      <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" spans="1:12">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2">
         <v>-113073.387</v>
@@ -4462,11 +4471,8 @@
       <c r="D3" s="2">
         <v>-55949.457000000002</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="I3" s="2">
         <v>-113097.88800000001</v>
@@ -4474,15 +4480,14 @@
       <c r="J3" s="2">
         <v>-55935.758000000002</v>
       </c>
-      <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1">
+    <row r="4" spans="1:12">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2">
         <v>-113052.853</v>
@@ -4490,11 +4495,8 @@
       <c r="D4" s="2">
         <v>-55849.837</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I4" s="2">
         <v>-113089.929</v>
@@ -4502,14 +4504,13 @@
       <c r="J4" s="2">
         <v>-55929.703000000001</v>
       </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2">
         <v>-113043.955</v>
@@ -4517,11 +4518,8 @@
       <c r="D5" s="2">
         <v>-55845.273999999998</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2">
         <v>-113072.197</v>
@@ -4529,19 +4527,13 @@
       <c r="J5" s="2">
         <v>-55839.353999999999</v>
       </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+        <v>116</v>
+      </c>
       <c r="H6" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I6" s="2">
         <v>-113076.753</v>
@@ -4549,30 +4541,11 @@
       <c r="J6" s="2">
         <v>-55830.451999999997</v>
       </c>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="8" spans="1:12" s="1" customFormat="1">
-      <c r="A8" s="3"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+    </row>
+    <row r="8" spans="1:12">
       <c r="L8" s="2"/>
     </row>
-    <row r="10" spans="1:12" s="1" customFormat="1">
-      <c r="A10" s="3"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+    <row r="10" spans="1:12">
       <c r="L10" s="2"/>
     </row>
   </sheetData>
@@ -4580,4 +4553,2978 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:L97"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="3.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" style="1" customWidth="1"/>
+    <col min="13" max="14" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="26" width="10.83203125" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2">
+        <v>-135097.54199999999</v>
+      </c>
+      <c r="D2" s="2">
+        <v>-76911.297000000006</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="2">
+        <v>-135068.87400000001</v>
+      </c>
+      <c r="J2" s="2">
+        <v>-76894.179000000004</v>
+      </c>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-135079.43</v>
+      </c>
+      <c r="D3" s="2">
+        <v>-76936.603000000003</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2">
+        <v>-135062.81200000001</v>
+      </c>
+      <c r="J3" s="2">
+        <v>-76903.524999999994</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2">
+        <v>-135060.79500000001</v>
+      </c>
+      <c r="D4" s="2">
+        <v>-76949.584000000003</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="2">
+        <v>-135069.38399999999</v>
+      </c>
+      <c r="J4" s="2">
+        <v>-76925.759000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2">
+        <v>-135039.13699999999</v>
+      </c>
+      <c r="D5" s="2">
+        <v>-76959.256999999998</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="2">
+        <v>-135060.766</v>
+      </c>
+      <c r="J5" s="2">
+        <v>-76933.748000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2">
+        <v>-135003.851</v>
+      </c>
+      <c r="D6" s="2">
+        <v>-76943.820000000007</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2">
+        <v>-135045.101</v>
+      </c>
+      <c r="J6" s="2">
+        <v>-76944.118000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2">
+        <v>-134969.17199999999</v>
+      </c>
+      <c r="D7" s="2">
+        <v>-76921.642000000007</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="2">
+        <v>-135033.06099999999</v>
+      </c>
+      <c r="J7" s="2">
+        <v>-76944.601999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-134947.65599999999</v>
+      </c>
+      <c r="D8" s="2">
+        <v>-76883.028000000006</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="2">
+        <v>-135006.364</v>
+      </c>
+      <c r="J8" s="2">
+        <v>-76932.725999999995</v>
+      </c>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="2">
+        <v>-134928.04399999999</v>
+      </c>
+      <c r="D9" s="2">
+        <v>-76861</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="2">
+        <v>-134981.39600000001</v>
+      </c>
+      <c r="J9" s="2">
+        <v>-76909.748000000007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="2">
+        <v>-134910.158</v>
+      </c>
+      <c r="D10" s="2">
+        <v>-76841.756999999998</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="2">
+        <v>-134962.14799999999</v>
+      </c>
+      <c r="J10" s="2">
+        <v>-76877.428</v>
+      </c>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="2">
+        <v>-134893.41</v>
+      </c>
+      <c r="D11" s="2">
+        <v>-76819.857000000004</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="2">
+        <v>-134933.20699999999</v>
+      </c>
+      <c r="J11" s="2">
+        <v>-76840.532999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="2">
+        <v>-134868.83100000001</v>
+      </c>
+      <c r="D12" s="2">
+        <v>-76789.835000000006</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="2">
+        <v>-134897.106</v>
+      </c>
+      <c r="J12" s="2">
+        <v>-76790.717000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2">
+        <v>-134838.234</v>
+      </c>
+      <c r="D13" s="2">
+        <v>-76755.085000000006</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="2">
+        <v>-134890.59299999999</v>
+      </c>
+      <c r="J13" s="2">
+        <v>-76764.100999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2">
+        <v>-134797.53599999999</v>
+      </c>
+      <c r="D14" s="2">
+        <v>-76739.834000000003</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="2">
+        <v>-134861.76500000001</v>
+      </c>
+      <c r="J14" s="2">
+        <v>-76742.061000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="2">
+        <v>-134771.52299999999</v>
+      </c>
+      <c r="D15" s="2">
+        <v>-76729.862999999998</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="2">
+        <v>-134834.978</v>
+      </c>
+      <c r="J15" s="2">
+        <v>-76728.606</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2">
+        <v>-134751.198</v>
+      </c>
+      <c r="D16" s="2">
+        <v>-76716.407999999996</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" s="2">
+        <v>-134801.97899999999</v>
+      </c>
+      <c r="J16" s="2">
+        <v>-76716.456999999995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="2">
+        <v>-134726.41800000001</v>
+      </c>
+      <c r="D17" s="2">
+        <v>-76707.391000000003</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="2">
+        <v>-134759.679</v>
+      </c>
+      <c r="J17" s="2">
+        <v>-76699.756999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="2">
+        <v>-134708.21799999999</v>
+      </c>
+      <c r="D18" s="2">
+        <v>-76695.870999999999</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="2">
+        <v>-134740.03400000001</v>
+      </c>
+      <c r="J18" s="2">
+        <v>-76687.282999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2">
+        <v>-134650.64600000001</v>
+      </c>
+      <c r="D19" s="2">
+        <v>-76665.634999999995</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="2">
+        <v>-134708.1</v>
+      </c>
+      <c r="J19" s="2">
+        <v>-76671.902000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="2">
+        <v>-134605.51199999999</v>
+      </c>
+      <c r="D20" s="2">
+        <v>-76659.659</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="2">
+        <v>-134685.23800000001</v>
+      </c>
+      <c r="J20" s="2">
+        <v>-76651.423999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="2">
+        <v>-134578.70499999999</v>
+      </c>
+      <c r="D21" s="2">
+        <v>-76647.652000000002</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I21" s="2">
+        <v>-134654.35699999999</v>
+      </c>
+      <c r="J21" s="2">
+        <v>-76644.884999999995</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="2">
+        <v>-134524.86900000001</v>
+      </c>
+      <c r="D22" s="2">
+        <v>-76633.850000000006</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I22" s="2">
+        <v>-134636.897</v>
+      </c>
+      <c r="J22" s="2">
+        <v>-76647.44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="2">
+        <v>-134496.74100000001</v>
+      </c>
+      <c r="D23" s="2">
+        <v>-76637.342999999993</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" s="2">
+        <v>-134572.40900000001</v>
+      </c>
+      <c r="J23" s="2">
+        <v>-76630.176999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="2">
+        <v>-134452.92800000001</v>
+      </c>
+      <c r="D24" s="2">
+        <v>-76645.001999999993</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I24" s="2">
+        <v>-134515.37899999999</v>
+      </c>
+      <c r="J24" s="2">
+        <v>-76611.504000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="2">
+        <v>-134438.06700000001</v>
+      </c>
+      <c r="D25" s="2">
+        <v>-76640.502999999997</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" s="2">
+        <v>-134468.71599999999</v>
+      </c>
+      <c r="J25" s="2">
+        <v>-76608.732999999993</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="2">
+        <v>-134419.81</v>
+      </c>
+      <c r="D26" s="2">
+        <v>-76648.27</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I26" s="2">
+        <v>-134420.851</v>
+      </c>
+      <c r="J26" s="2">
+        <v>-76620.320999999996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="2">
+        <v>-134407.47700000001</v>
+      </c>
+      <c r="D27" s="2">
+        <v>-76657.409</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I27" s="2">
+        <v>-134386.86199999999</v>
+      </c>
+      <c r="J27" s="2">
+        <v>-76636.864000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="2">
+        <v>-134390.323</v>
+      </c>
+      <c r="D28" s="2">
+        <v>-76667.065000000002</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I28" s="2">
+        <v>-134346.98199999999</v>
+      </c>
+      <c r="J28" s="2">
+        <v>-76666.062000000005</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="2">
+        <v>-134353.185</v>
+      </c>
+      <c r="D29" s="2">
+        <v>-76690.694000000003</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I29" s="2">
+        <v>-134311.307</v>
+      </c>
+      <c r="J29" s="2">
+        <v>-76691.918999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="2">
+        <v>-134319.234</v>
+      </c>
+      <c r="D30" s="2">
+        <v>-76726.668000000005</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I30" s="2">
+        <v>-134290.00200000001</v>
+      </c>
+      <c r="J30" s="2">
+        <v>-76691.918999999994</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="2">
+        <v>-134319.234</v>
+      </c>
+      <c r="D31" s="2">
+        <v>-76750.38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="2">
+        <v>-134229.51500000001</v>
+      </c>
+      <c r="D33" s="2">
+        <v>-76777.911999999997</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I33" s="2">
+        <v>-134242.75899999999</v>
+      </c>
+      <c r="J33" s="2">
+        <v>-76742.505000000005</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="2">
+        <v>-134211.81899999999</v>
+      </c>
+      <c r="D34" s="2">
+        <v>-76801.555999999997</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I34" s="2">
+        <v>-134223.25599999999</v>
+      </c>
+      <c r="J34" s="2">
+        <v>-76761.012000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="2">
+        <v>-134152.446</v>
+      </c>
+      <c r="D35" s="2">
+        <v>-76818.81</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I35" s="2">
+        <v>-134195.49900000001</v>
+      </c>
+      <c r="J35" s="2">
+        <v>-76780.350000000006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="2">
+        <v>-134094.473</v>
+      </c>
+      <c r="D36" s="2">
+        <v>-76793.762000000002</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36" s="2">
+        <v>-134165.853</v>
+      </c>
+      <c r="J36" s="2">
+        <v>-76788.406000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="2">
+        <v>-134078.397</v>
+      </c>
+      <c r="D37" s="2">
+        <v>-76798.514999999999</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I37" s="2">
+        <v>-134166.43599999999</v>
+      </c>
+      <c r="J37" s="2">
+        <v>-76781.167000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="2">
+        <v>-134056.98000000001</v>
+      </c>
+      <c r="D38" s="2">
+        <v>-76777.142000000007</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I38" s="2">
+        <v>-134132.72</v>
+      </c>
+      <c r="J38" s="2">
+        <v>-76759.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="2">
+        <v>-134050.85800000001</v>
+      </c>
+      <c r="D39" s="2">
+        <v>-76754.951000000001</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I39" s="2">
+        <v>-134110.04300000001</v>
+      </c>
+      <c r="J39" s="2">
+        <v>-76729.376000000004</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="2">
+        <v>-134026.185</v>
+      </c>
+      <c r="D40" s="2">
+        <v>-76741.279999999999</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I40" s="2">
+        <v>-134070.92199999999</v>
+      </c>
+      <c r="J40" s="2">
+        <v>-76745.981</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="2">
+        <v>-134006.62100000001</v>
+      </c>
+      <c r="D41" s="2">
+        <v>-76726.304000000004</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I41" s="2">
+        <v>-134008.16699999999</v>
+      </c>
+      <c r="J41" s="2">
+        <v>-76696.895000000004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="2">
+        <v>-133972.78200000001</v>
+      </c>
+      <c r="D42" s="2">
+        <v>-76692.668000000005</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I42" s="2">
+        <v>-134011.45199999999</v>
+      </c>
+      <c r="J42" s="2">
+        <v>-76683.547999999995</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" s="2">
+        <v>-133929.39000000001</v>
+      </c>
+      <c r="D43" s="2">
+        <v>-76660.573999999993</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I43" s="2">
+        <v>-133993.06</v>
+      </c>
+      <c r="J43" s="2">
+        <v>-76675.275999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="2">
+        <v>-133895.353</v>
+      </c>
+      <c r="D44" s="2">
+        <v>-76632.995999999999</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I44" s="2">
+        <v>-133989.253</v>
+      </c>
+      <c r="J44" s="2">
+        <v>-76683.327000000005</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="2">
+        <v>-133860.01300000001</v>
+      </c>
+      <c r="D45" s="2">
+        <v>-76590.588000000003</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I45" s="2">
+        <v>-133938.37899999999</v>
+      </c>
+      <c r="J45" s="2">
+        <v>-76645.486000000004</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="2">
+        <v>-133847.53700000001</v>
+      </c>
+      <c r="D46" s="2">
+        <v>-76563.756999999998</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I46" s="2">
+        <v>-133905.49799999999</v>
+      </c>
+      <c r="J46" s="2">
+        <v>-76613.168000000005</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="2">
+        <v>-133829.63699999999</v>
+      </c>
+      <c r="D47" s="2">
+        <v>-76544.281000000003</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I47" s="2">
+        <v>-133884.02900000001</v>
+      </c>
+      <c r="J47" s="2">
+        <v>-76578.487999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="2">
+        <v>-133829.527</v>
+      </c>
+      <c r="D48" s="2">
+        <v>-76515.085000000006</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I48" s="2">
+        <v>-133869.79699999999</v>
+      </c>
+      <c r="J48" s="2">
+        <v>-76575.159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="2">
+        <v>-133815.954</v>
+      </c>
+      <c r="D49" s="2">
+        <v>-76496.044999999998</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I49" s="2">
+        <v>-133861.011</v>
+      </c>
+      <c r="J49" s="2">
+        <v>-76550.558999999994</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="2">
+        <v>-133805.49100000001</v>
+      </c>
+      <c r="D50" s="2">
+        <v>-76475.247000000003</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I50" s="2">
+        <v>-133858.905</v>
+      </c>
+      <c r="J50" s="2">
+        <v>-76532.456999999995</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="2">
+        <v>-133799.65700000001</v>
+      </c>
+      <c r="D51" s="2">
+        <v>-76459.396999999997</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I51" s="2">
+        <v>-133871.03400000001</v>
+      </c>
+      <c r="J51" s="2">
+        <v>-76521.987999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="2">
+        <v>-133795.177</v>
+      </c>
+      <c r="D52" s="2">
+        <v>-76443.410999999993</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I52" s="2">
+        <v>-133877.04300000001</v>
+      </c>
+      <c r="J52" s="2">
+        <v>-76497.803</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C53" s="2">
+        <v>-133786.424</v>
+      </c>
+      <c r="D53" s="2">
+        <v>-76424.618000000002</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I53" s="2">
+        <v>-133855.81299999999</v>
+      </c>
+      <c r="J53" s="2">
+        <v>-76505.027000000002</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="2">
+        <v>-133774.23000000001</v>
+      </c>
+      <c r="D54" s="2">
+        <v>-76393.718999999997</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I54" s="2">
+        <v>-133853.85200000001</v>
+      </c>
+      <c r="J54" s="2">
+        <v>-76465.534</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C55" s="2">
+        <v>-133764.93599999999</v>
+      </c>
+      <c r="D55" s="2">
+        <v>-76361.981</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I55" s="2">
+        <v>-133858.87700000001</v>
+      </c>
+      <c r="J55" s="2">
+        <v>-76430.736000000004</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C56" s="2">
+        <v>-133750.40900000001</v>
+      </c>
+      <c r="D56" s="2">
+        <v>-76329.620999999999</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I56" s="2">
+        <v>-133848.38500000001</v>
+      </c>
+      <c r="J56" s="2">
+        <v>-76387.502999999997</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" s="2">
+        <v>-133732.22500000001</v>
+      </c>
+      <c r="D57" s="2">
+        <v>-76307.370999999999</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I57" s="2">
+        <v>-133841.416</v>
+      </c>
+      <c r="J57" s="2">
+        <v>-76350.998999999996</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="2">
+        <v>-133723.94</v>
+      </c>
+      <c r="D58" s="2">
+        <v>-76288.476999999999</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I58" s="2">
+        <v>-133834.58900000001</v>
+      </c>
+      <c r="J58" s="2">
+        <v>-76344.606</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59" s="2">
+        <v>-133710.435</v>
+      </c>
+      <c r="D59" s="2">
+        <v>-76272.313999999998</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I59" s="2">
+        <v>-133821.03200000001</v>
+      </c>
+      <c r="J59" s="2">
+        <v>-76335.823000000004</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C60" s="2">
+        <v>-133702.55300000001</v>
+      </c>
+      <c r="D60" s="2">
+        <v>-76259.974000000002</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I60" s="2">
+        <v>-133797.23000000001</v>
+      </c>
+      <c r="J60" s="2">
+        <v>-76351.19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" s="2">
+        <v>-133697.62</v>
+      </c>
+      <c r="D61" s="2">
+        <v>-76243.016000000003</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I61" s="2">
+        <v>-133791.92300000001</v>
+      </c>
+      <c r="J61" s="2">
+        <v>-76333.036999999997</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I62" s="2">
+        <v>-133771.921</v>
+      </c>
+      <c r="J62" s="2">
+        <v>-76302.77</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I63" s="2">
+        <v>-133746.85500000001</v>
+      </c>
+      <c r="J63" s="2">
+        <v>-76271.464999999997</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I64" s="2">
+        <v>-133734.53700000001</v>
+      </c>
+      <c r="J64" s="2">
+        <v>-76243.851999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C66" s="2">
+        <v>-133689.25099999999</v>
+      </c>
+      <c r="D66" s="2">
+        <v>-76208.565000000002</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I66" s="2">
+        <v>-133703.277</v>
+      </c>
+      <c r="J66" s="2">
+        <v>-76194.402000000002</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C67" s="2">
+        <v>-133660.353</v>
+      </c>
+      <c r="D67" s="2">
+        <v>-76158.266000000003</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I67" s="2">
+        <v>-133695.84299999999</v>
+      </c>
+      <c r="J67" s="2">
+        <v>-76169.703999999998</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C68" s="2">
+        <v>-133652.18299999999</v>
+      </c>
+      <c r="D68" s="2">
+        <v>-76138.819000000003</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I68" s="2">
+        <v>-133681.198</v>
+      </c>
+      <c r="J68" s="2">
+        <v>-76159.978000000003</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C69" s="2">
+        <v>-133637.36900000001</v>
+      </c>
+      <c r="D69" s="2">
+        <v>-76133.256999999998</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I69" s="2">
+        <v>-133655.424</v>
+      </c>
+      <c r="J69" s="2">
+        <v>-76116.077000000005</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C70" s="2">
+        <v>-133619.68100000001</v>
+      </c>
+      <c r="D70" s="2">
+        <v>-76120.563999999998</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I70" s="2">
+        <v>-133631.40700000001</v>
+      </c>
+      <c r="J70" s="2">
+        <v>-76089.654999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C71" s="2">
+        <v>-133602.649</v>
+      </c>
+      <c r="D71" s="2">
+        <v>-76108.111999999994</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I71" s="2">
+        <v>-133605.223</v>
+      </c>
+      <c r="J71" s="2">
+        <v>-76057.440000000002</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C72" s="2">
+        <v>-133593.33100000001</v>
+      </c>
+      <c r="D72" s="2">
+        <v>-76094.603000000003</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I72" s="2">
+        <v>-133578.65299999999</v>
+      </c>
+      <c r="J72" s="2">
+        <v>-76051.948999999993</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C73" s="2">
+        <v>-133563.51</v>
+      </c>
+      <c r="D73" s="2">
+        <v>-76088.952999999994</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I73" s="2">
+        <v>-133539.15900000001</v>
+      </c>
+      <c r="J73" s="2">
+        <v>-76064.850000000006</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C74" s="2">
+        <v>-133544.04399999999</v>
+      </c>
+      <c r="D74" s="2">
+        <v>-76085.907000000007</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I74" s="2">
+        <v>-133502.136</v>
+      </c>
+      <c r="J74" s="2">
+        <v>-76076.297000000006</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C75" s="2">
+        <v>-133487.1</v>
+      </c>
+      <c r="D75" s="2">
+        <v>-76100.308000000005</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I75" s="2">
+        <v>-133464.66399999999</v>
+      </c>
+      <c r="J75" s="2">
+        <v>-76092.149000000005</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C76" s="2">
+        <v>-133456.74100000001</v>
+      </c>
+      <c r="D76" s="2">
+        <v>-76113.350000000006</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I76" s="2">
+        <v>-133432.935</v>
+      </c>
+      <c r="J76" s="2">
+        <v>-76102.808999999994</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C77" s="2">
+        <v>-133442.33199999999</v>
+      </c>
+      <c r="D77" s="2">
+        <v>-76130.881999999998</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I77" s="2">
+        <v>-133405.60500000001</v>
+      </c>
+      <c r="J77" s="2">
+        <v>-76128.626999999993</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C78" s="2">
+        <v>-133425.84</v>
+      </c>
+      <c r="D78" s="2">
+        <v>-76137.790999999997</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I78" s="2">
+        <v>-133388.13200000001</v>
+      </c>
+      <c r="J78" s="2">
+        <v>-76152.216</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C79" s="2">
+        <v>-133402.40599999999</v>
+      </c>
+      <c r="D79" s="2">
+        <v>-76172.381999999998</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I79" s="2">
+        <v>-133358.54300000001</v>
+      </c>
+      <c r="J79" s="2">
+        <v>-76196.577999999994</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C80" s="2">
+        <v>-133386.81899999999</v>
+      </c>
+      <c r="D80" s="2">
+        <v>-76198.843999999997</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I80" s="2">
+        <v>-133328.592</v>
+      </c>
+      <c r="J80" s="2">
+        <v>-76222.498999999996</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C81" s="2">
+        <v>-133361.291</v>
+      </c>
+      <c r="D81" s="2">
+        <v>-76218.475000000006</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I81" s="2">
+        <v>-133293.93799999999</v>
+      </c>
+      <c r="J81" s="2">
+        <v>-76243.377999999997</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C82" s="2">
+        <v>-133336.67300000001</v>
+      </c>
+      <c r="D82" s="2">
+        <v>-76240.308000000005</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I82" s="2">
+        <v>-133265.087</v>
+      </c>
+      <c r="J82" s="2">
+        <v>-76258.52</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C83" s="2">
+        <v>-133303.64000000001</v>
+      </c>
+      <c r="D83" s="2">
+        <v>-76260.873000000007</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I83" s="2">
+        <v>-133247.82699999999</v>
+      </c>
+      <c r="J83" s="2">
+        <v>-76257.231</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C84" s="2">
+        <v>-133268.639</v>
+      </c>
+      <c r="D84" s="2">
+        <v>-76274.789999999994</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I84" s="2">
+        <v>-133211.245</v>
+      </c>
+      <c r="J84" s="2">
+        <v>-76261.789000000004</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C85" s="2">
+        <v>-133221.17300000001</v>
+      </c>
+      <c r="D85" s="2">
+        <v>-76281.629000000001</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I85" s="2">
+        <v>-133180.06099999999</v>
+      </c>
+      <c r="J85" s="2">
+        <v>-76257.850999999995</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C86" s="2">
+        <v>-133171.56099999999</v>
+      </c>
+      <c r="D86" s="2">
+        <v>-76279.494000000006</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I86" s="2">
+        <v>-133133.603</v>
+      </c>
+      <c r="J86" s="2">
+        <v>-76246.046000000002</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C87" s="2">
+        <v>-133111.658</v>
+      </c>
+      <c r="D87" s="2">
+        <v>-76264.42</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I87" s="2">
+        <v>-133104.011</v>
+      </c>
+      <c r="J87" s="2">
+        <v>-76235.434999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C88" s="2">
+        <v>-133097.348</v>
+      </c>
+      <c r="D88" s="2">
+        <v>-76327.909</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I88" s="2">
+        <v>-133057.75700000001</v>
+      </c>
+      <c r="J88" s="2">
+        <v>-76226.945000000007</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C89" s="2">
+        <v>-133095.136</v>
+      </c>
+      <c r="D89" s="2">
+        <v>-76345.866999999998</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I89" s="2">
+        <v>-133035.14799999999</v>
+      </c>
+      <c r="J89" s="2">
+        <v>-76222.562000000005</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C90" s="2">
+        <v>-133099.30900000001</v>
+      </c>
+      <c r="D90" s="2">
+        <v>-76360.046000000002</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I90" s="2">
+        <v>-133004.891</v>
+      </c>
+      <c r="J90" s="2">
+        <v>-76214.021999999997</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C91" s="2">
+        <v>-133080.08499999999</v>
+      </c>
+      <c r="D91" s="2">
+        <v>-76359.267999999996</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I91" s="2">
+        <v>-132991.95800000001</v>
+      </c>
+      <c r="J91" s="2">
+        <v>-76209.25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C92" s="2">
+        <v>-133084.94200000001</v>
+      </c>
+      <c r="D92" s="2">
+        <v>-76345.398000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C93" s="2">
+        <v>-133087.57399999999</v>
+      </c>
+      <c r="D93" s="2">
+        <v>-76326.17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C94" s="2">
+        <v>-133101.448</v>
+      </c>
+      <c r="D94" s="2">
+        <v>-76262.3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C95" s="2">
+        <v>-133060.62400000001</v>
+      </c>
+      <c r="D95" s="2">
+        <v>-76253.316000000006</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C96" s="2">
+        <v>-133021.98199999999</v>
+      </c>
+      <c r="D96" s="2">
+        <v>-76244.710999999996</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C97" s="2">
+        <v>-132985.818</v>
+      </c>
+      <c r="D97" s="2">
+        <v>-76236.039000000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <cols>
+    <col min="1" max="14" width="16.83203125" style="3" customWidth="1"/>
+    <col min="15" max="23" width="10.83203125" style="3" customWidth="1"/>
+    <col min="24" max="16384" width="10.83203125" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="B1" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2">
+        <v>-133861.011</v>
+      </c>
+      <c r="I2">
+        <v>-76550.558999999994</v>
+      </c>
+      <c r="J2">
+        <v>-133815.954</v>
+      </c>
+      <c r="K2">
+        <v>-76496.044999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H3">
+        <v>-133858.905</v>
+      </c>
+      <c r="I3">
+        <v>-76532.456999999995</v>
+      </c>
+      <c r="J3">
+        <v>-133805.49100000001</v>
+      </c>
+      <c r="K3">
+        <v>-76475.247000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" t="s">
+        <v>218</v>
+      </c>
+      <c r="G4" t="s">
+        <v>219</v>
+      </c>
+      <c r="H4">
+        <v>-133871.03400000001</v>
+      </c>
+      <c r="I4">
+        <v>-76521.987999999998</v>
+      </c>
+      <c r="J4">
+        <v>-133799.65700000001</v>
+      </c>
+      <c r="K4">
+        <v>-76459.396999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H5">
+        <v>-133877.04300000001</v>
+      </c>
+      <c r="I5">
+        <v>-76497.803</v>
+      </c>
+      <c r="J5">
+        <v>-133795.177</v>
+      </c>
+      <c r="K5">
+        <v>-76443.410999999993</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" t="s">
+        <v>226</v>
+      </c>
+      <c r="G6" t="s">
+        <v>227</v>
+      </c>
+      <c r="H6">
+        <v>-133855.81299999999</v>
+      </c>
+      <c r="I6">
+        <v>-76505.027000000002</v>
+      </c>
+      <c r="J6">
+        <v>-133786.424</v>
+      </c>
+      <c r="K6">
+        <v>-76424.618000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" t="s">
+        <v>230</v>
+      </c>
+      <c r="G7" t="s">
+        <v>231</v>
+      </c>
+      <c r="H7">
+        <v>-133853.85200000001</v>
+      </c>
+      <c r="I7">
+        <v>-76465.534</v>
+      </c>
+      <c r="J7">
+        <v>-133774.23000000001</v>
+      </c>
+      <c r="K7">
+        <v>-76393.718999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" t="s">
+        <v>235</v>
+      </c>
+      <c r="H8">
+        <v>-133858.87700000001</v>
+      </c>
+      <c r="I8">
+        <v>-76430.736000000004</v>
+      </c>
+      <c r="J8">
+        <v>-133764.93599999999</v>
+      </c>
+      <c r="K8">
+        <v>-76361.981</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" t="s">
+        <v>238</v>
+      </c>
+      <c r="G9" t="s">
+        <v>239</v>
+      </c>
+      <c r="H9">
+        <v>-133848.38500000001</v>
+      </c>
+      <c r="I9">
+        <v>-76387.502999999997</v>
+      </c>
+      <c r="J9">
+        <v>-133750.40900000001</v>
+      </c>
+      <c r="K9">
+        <v>-76329.620999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C10" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" t="s">
+        <v>242</v>
+      </c>
+      <c r="G10" t="s">
+        <v>243</v>
+      </c>
+      <c r="H10">
+        <v>-133841.416</v>
+      </c>
+      <c r="I10">
+        <v>-76350.998999999996</v>
+      </c>
+      <c r="J10">
+        <v>-133732.22500000001</v>
+      </c>
+      <c r="K10">
+        <v>-76307.370999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>244</v>
+      </c>
+      <c r="B11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" t="s">
+        <v>246</v>
+      </c>
+      <c r="E11" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" t="s">
+        <v>247</v>
+      </c>
+      <c r="G11" t="s">
+        <v>248</v>
+      </c>
+      <c r="H11">
+        <v>-133834.58900000001</v>
+      </c>
+      <c r="I11">
+        <v>-76344.606</v>
+      </c>
+      <c r="J11">
+        <v>-133723.94</v>
+      </c>
+      <c r="K11">
+        <v>-76288.476999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" t="s">
+        <v>250</v>
+      </c>
+      <c r="E12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12" t="s">
+        <v>251</v>
+      </c>
+      <c r="G12" t="s">
+        <v>252</v>
+      </c>
+      <c r="H12">
+        <v>-133821.03200000001</v>
+      </c>
+      <c r="I12">
+        <v>-76335.823000000004</v>
+      </c>
+      <c r="J12">
+        <v>-133710.435</v>
+      </c>
+      <c r="K12">
+        <v>-76272.313999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" t="s">
+        <v>255</v>
+      </c>
+      <c r="G13" t="s">
+        <v>256</v>
+      </c>
+      <c r="H13">
+        <v>-133797.23000000001</v>
+      </c>
+      <c r="I13">
+        <v>-76351.19</v>
+      </c>
+      <c r="J13">
+        <v>-133702.55300000001</v>
+      </c>
+      <c r="K13">
+        <v>-76259.974000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C14" t="s">
+        <v>258</v>
+      </c>
+      <c r="E14" t="s">
+        <v>139</v>
+      </c>
+      <c r="F14" t="s">
+        <v>259</v>
+      </c>
+      <c r="G14" t="s">
+        <v>260</v>
+      </c>
+      <c r="H14">
+        <v>-133791.92300000001</v>
+      </c>
+      <c r="I14">
+        <v>-76333.036999999997</v>
+      </c>
+      <c r="J14">
+        <v>-133697.62</v>
+      </c>
+      <c r="K14">
+        <v>-76243.016000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" t="s">
+        <v>262</v>
+      </c>
+      <c r="H15">
+        <v>-133771.921</v>
+      </c>
+      <c r="I15">
+        <v>-76302.77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C16" t="s">
+        <v>264</v>
+      </c>
+      <c r="H16">
+        <v>-133746.85500000001</v>
+      </c>
+      <c r="I16">
+        <v>-76271.464999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" t="s">
+        <v>265</v>
+      </c>
+      <c r="C17" t="s">
+        <v>266</v>
+      </c>
+      <c r="H17">
+        <v>-133734.53700000001</v>
+      </c>
+      <c r="I17">
+        <v>-76243.851999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>